--- a/CLIMATIZACAO_MODELO_CONSOLIDADO.xlsx
+++ b/CLIMATIZACAO_MODELO_CONSOLIDADO.xlsx
@@ -7835,10 +7835,10 @@
         <v>45</v>
       </c>
       <c r="V2" s="5" t="n">
-        <v>-3.7133858</v>
+        <v>-3.713386</v>
       </c>
       <c r="W2" s="5" t="n">
-        <v>-38.5544973</v>
+        <v>-38.554497</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7893,8 +7893,12 @@
       <c r="U3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
+      <c r="V3" s="5" t="n">
+        <v>-3.718986</v>
+      </c>
+      <c r="W3" s="5" t="n">
+        <v>-38.54702</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
@@ -7949,10 +7953,10 @@
         <v>59</v>
       </c>
       <c r="V4" s="5" t="n">
-        <v>-3.8005587</v>
+        <v>-3.800559</v>
       </c>
       <c r="W4" s="5" t="n">
-        <v>-38.4497099</v>
+        <v>-38.44971</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8010,10 +8014,10 @@
         <v>66</v>
       </c>
       <c r="V5" s="5" t="n">
-        <v>-3.807992</v>
+        <v>-3.808954</v>
       </c>
       <c r="W5" s="5" t="n">
-        <v>-38.5925545</v>
+        <v>-38.587679</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8071,10 +8075,10 @@
         <v>72</v>
       </c>
       <c r="V6" s="5" t="n">
-        <v>-3.8364734</v>
+        <v>-3.838117</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>-38.55736</v>
+        <v>-38.558172</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8132,10 +8136,10 @@
         <v>77</v>
       </c>
       <c r="V7" s="5" t="n">
-        <v>-3.8009694</v>
+        <v>-3.799274</v>
       </c>
       <c r="W7" s="5" t="n">
-        <v>-38.5608537</v>
+        <v>-38.562127</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8193,10 +8197,10 @@
         <v>82</v>
       </c>
       <c r="V8" s="5" t="n">
-        <v>-3.7933959</v>
+        <v>-3.790799</v>
       </c>
       <c r="W8" s="5" t="n">
-        <v>-38.6137736</v>
+        <v>-38.618999</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8254,10 +8258,10 @@
         <v>86</v>
       </c>
       <c r="V9" s="5" t="n">
-        <v>-3.7925828</v>
+        <v>-3.792902</v>
       </c>
       <c r="W9" s="5" t="n">
-        <v>-38.6257333</v>
+        <v>-38.62517</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8315,10 +8319,10 @@
         <v>91</v>
       </c>
       <c r="V10" s="5" t="n">
-        <v>-3.7649452</v>
+        <v>-3.764955</v>
       </c>
       <c r="W10" s="5" t="n">
-        <v>-38.4402285</v>
+        <v>-38.440217</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8378,10 +8382,10 @@
         <v>98</v>
       </c>
       <c r="V11" s="5" t="n">
-        <v>-3.7640916</v>
+        <v>-3.764402</v>
       </c>
       <c r="W11" s="5" t="n">
-        <v>-38.563127</v>
+        <v>-38.563139</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8439,10 +8443,10 @@
         <v>103</v>
       </c>
       <c r="V12" s="5" t="n">
-        <v>-3.7375332</v>
+        <v>-3.737453</v>
       </c>
       <c r="W12" s="5" t="n">
-        <v>-38.5983711</v>
+        <v>-38.598841</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8500,10 +8504,10 @@
         <v>108</v>
       </c>
       <c r="V13" s="5" t="n">
-        <v>-3.8310728</v>
+        <v>-3.831197</v>
       </c>
       <c r="W13" s="5" t="n">
-        <v>-38.5711175</v>
+        <v>-38.570365</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8561,10 +8565,10 @@
         <v>113</v>
       </c>
       <c r="V14" s="5" t="n">
-        <v>-3.8145367</v>
+        <v>-3.814541</v>
       </c>
       <c r="W14" s="5" t="n">
-        <v>-38.5234599</v>
+        <v>-38.523522</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8621,8 +8625,12 @@
       <c r="U15" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="V15" s="5"/>
-      <c r="W15" s="5"/>
+      <c r="V15" s="5" t="n">
+        <v>-3.803541</v>
+      </c>
+      <c r="W15" s="5" t="n">
+        <v>-38.585469</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5" t="s">
@@ -8679,10 +8687,10 @@
         <v>122</v>
       </c>
       <c r="V16" s="5" t="n">
-        <v>-3.7060494</v>
+        <v>-3.70541</v>
       </c>
       <c r="W16" s="5" t="n">
-        <v>-38.563909</v>
+        <v>-38.563573</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8740,10 +8748,10 @@
         <v>127</v>
       </c>
       <c r="V17" s="5" t="n">
-        <v>-3.8000712</v>
+        <v>-3.794198</v>
       </c>
       <c r="W17" s="5" t="n">
-        <v>-38.5571755</v>
+        <v>-38.553844</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8801,10 +8809,10 @@
         <v>132</v>
       </c>
       <c r="V18" s="5" t="n">
-        <v>-3.8008803</v>
+        <v>-3.800876</v>
       </c>
       <c r="W18" s="5" t="n">
-        <v>-38.5180241</v>
+        <v>-38.518016</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8862,10 +8870,10 @@
         <v>137</v>
       </c>
       <c r="V19" s="5" t="n">
-        <v>-3.7634547</v>
+        <v>-3.763354</v>
       </c>
       <c r="W19" s="5" t="n">
-        <v>-38.5341285</v>
+        <v>-38.534471</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8923,10 +8931,10 @@
         <v>142</v>
       </c>
       <c r="V20" s="5" t="n">
-        <v>-3.7572552</v>
+        <v>-3.757481</v>
       </c>
       <c r="W20" s="5" t="n">
-        <v>-38.5658267</v>
+        <v>-38.565738</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8984,10 +8992,10 @@
         <v>147</v>
       </c>
       <c r="V21" s="5" t="n">
-        <v>-3.7657365</v>
+        <v>-3.761867</v>
       </c>
       <c r="W21" s="5" t="n">
-        <v>-38.5502281</v>
+        <v>-38.554918</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9045,10 +9053,10 @@
         <v>152</v>
       </c>
       <c r="V22" s="5" t="n">
-        <v>-3.7560149</v>
+        <v>-3.756015</v>
       </c>
       <c r="W22" s="5" t="n">
-        <v>-38.5066083</v>
+        <v>-38.506608</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9106,10 +9114,10 @@
         <v>157</v>
       </c>
       <c r="V23" s="5" t="n">
-        <v>-3.7091052</v>
+        <v>-3.709538</v>
       </c>
       <c r="W23" s="5" t="n">
-        <v>-38.5819017</v>
+        <v>-38.582291</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9167,10 +9175,10 @@
         <v>162</v>
       </c>
       <c r="V24" s="5" t="n">
-        <v>-3.7818646</v>
+        <v>-3.781879</v>
       </c>
       <c r="W24" s="5" t="n">
-        <v>-38.6022554</v>
+        <v>-38.602251</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9227,8 +9235,12 @@
       <c r="U25" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
+      <c r="V25" s="5" t="n">
+        <v>-3.799248</v>
+      </c>
+      <c r="W25" s="5" t="n">
+        <v>-38.5468</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="s">
@@ -9284,8 +9296,12 @@
       <c r="U26" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="V26" s="5"/>
-      <c r="W26" s="5"/>
+      <c r="V26" s="5" t="n">
+        <v>-3.82567</v>
+      </c>
+      <c r="W26" s="5" t="n">
+        <v>-38.581063</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
@@ -9342,7 +9358,7 @@
         <v>176</v>
       </c>
       <c r="V27" s="5" t="n">
-        <v>-3.7891972</v>
+        <v>-3.789197</v>
       </c>
       <c r="W27" s="5" t="n">
         <v>-38.629868</v>
@@ -9403,10 +9419,10 @@
         <v>181</v>
       </c>
       <c r="V28" s="5" t="n">
-        <v>-3.7247791</v>
+        <v>-3.725356</v>
       </c>
       <c r="W28" s="5" t="n">
-        <v>-38.5724916</v>
+        <v>-38.572991</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9464,10 +9480,10 @@
         <v>186</v>
       </c>
       <c r="V29" s="5" t="n">
-        <v>-3.7247246</v>
+        <v>-3.722707</v>
       </c>
       <c r="W29" s="5" t="n">
-        <v>-38.556485</v>
+        <v>-38.557239</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9524,8 +9540,12 @@
       <c r="U30" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="V30" s="5"/>
-      <c r="W30" s="5"/>
+      <c r="V30" s="5" t="n">
+        <v>-3.772013</v>
+      </c>
+      <c r="W30" s="5" t="n">
+        <v>-38.479501</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5" t="s">
@@ -9582,10 +9602,10 @@
         <v>195</v>
       </c>
       <c r="V31" s="5" t="n">
-        <v>-3.7108678</v>
+        <v>-3.71085</v>
       </c>
       <c r="W31" s="5" t="n">
-        <v>-38.5674413</v>
+        <v>-38.567494</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9643,10 +9663,10 @@
         <v>200</v>
       </c>
       <c r="V32" s="5" t="n">
-        <v>-3.7198691</v>
+        <v>-3.720008</v>
       </c>
       <c r="W32" s="5" t="n">
-        <v>-38.6060014</v>
+        <v>-38.606297</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9704,10 +9724,10 @@
         <v>205</v>
       </c>
       <c r="V33" s="5" t="n">
-        <v>-3.7386914</v>
+        <v>-3.738674</v>
       </c>
       <c r="W33" s="5" t="n">
-        <v>-38.5944852</v>
+        <v>-38.595788</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9764,8 +9784,12 @@
       <c r="U34" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="V34" s="5"/>
-      <c r="W34" s="5"/>
+      <c r="V34" s="5" t="n">
+        <v>-3.817595</v>
+      </c>
+      <c r="W34" s="5" t="n">
+        <v>-38.569756</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5" t="s">
@@ -9822,10 +9846,10 @@
         <v>214</v>
       </c>
       <c r="V35" s="5" t="n">
-        <v>-3.7924238</v>
+        <v>-3.792099</v>
       </c>
       <c r="W35" s="5" t="n">
-        <v>-38.5382055</v>
+        <v>-38.537916</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9883,10 +9907,10 @@
         <v>219</v>
       </c>
       <c r="V36" s="5" t="n">
-        <v>-3.783015</v>
+        <v>-3.782699</v>
       </c>
       <c r="W36" s="5" t="n">
-        <v>-38.5424879</v>
+        <v>-38.542618</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9944,10 +9968,10 @@
         <v>223</v>
       </c>
       <c r="V37" s="5" t="n">
-        <v>-3.7843707</v>
+        <v>-3.784358</v>
       </c>
       <c r="W37" s="5" t="n">
-        <v>-38.6271744</v>
+        <v>-38.627182</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10004,8 +10028,12 @@
       <c r="U38" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="V38" s="5"/>
-      <c r="W38" s="5"/>
+      <c r="V38" s="5" t="n">
+        <v>-3.80653</v>
+      </c>
+      <c r="W38" s="5" t="n">
+        <v>-38.569252</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5" t="s">
@@ -10062,10 +10090,10 @@
         <v>232</v>
       </c>
       <c r="V39" s="5" t="n">
-        <v>-3.8141051</v>
+        <v>-3.814123</v>
       </c>
       <c r="W39" s="5" t="n">
-        <v>-38.5912634</v>
+        <v>-38.591263</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10122,8 +10150,12 @@
       <c r="U40" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="V40" s="5"/>
-      <c r="W40" s="5"/>
+      <c r="V40" s="5" t="n">
+        <v>-3.829354</v>
+      </c>
+      <c r="W40" s="5" t="n">
+        <v>-38.590225</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5" t="s">
@@ -10178,10 +10210,10 @@
         <v>242</v>
       </c>
       <c r="V41" s="5" t="n">
-        <v>-3.7776952</v>
+        <v>-3.777714</v>
       </c>
       <c r="W41" s="5" t="n">
-        <v>-38.559468</v>
+        <v>-38.559507</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10237,10 +10269,10 @@
         <v>247</v>
       </c>
       <c r="V42" s="5" t="n">
-        <v>-3.7379747</v>
+        <v>-3.737842</v>
       </c>
       <c r="W42" s="5" t="n">
-        <v>-38.4565172</v>
+        <v>-38.45653</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10296,10 +10328,10 @@
         <v>251</v>
       </c>
       <c r="V43" s="5" t="n">
-        <v>-3.7091719</v>
+        <v>-3.709081</v>
       </c>
       <c r="W43" s="5" t="n">
-        <v>-38.5804059</v>
+        <v>-38.580808</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10355,10 +10387,10 @@
         <v>255</v>
       </c>
       <c r="V44" s="5" t="n">
-        <v>-3.7664338</v>
+        <v>-3.766432</v>
       </c>
       <c r="W44" s="5" t="n">
-        <v>-38.5361866</v>
+        <v>-38.536173</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10413,8 +10445,12 @@
       <c r="U45" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="V45" s="5"/>
-      <c r="W45" s="5"/>
+      <c r="V45" s="5" t="n">
+        <v>-3.813607</v>
+      </c>
+      <c r="W45" s="5" t="n">
+        <v>-38.595816</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5" t="s">
@@ -10468,8 +10504,12 @@
       <c r="U46" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="V46" s="5"/>
-      <c r="W46" s="5"/>
+      <c r="V46" s="5" t="n">
+        <v>-3.718023</v>
+      </c>
+      <c r="W46" s="5" t="n">
+        <v>-38.600136</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5" t="s">
@@ -10524,10 +10564,10 @@
         <v>268</v>
       </c>
       <c r="V47" s="5" t="n">
-        <v>-3.7309843</v>
+        <v>-3.727524</v>
       </c>
       <c r="W47" s="5" t="n">
-        <v>-38.5587561</v>
+        <v>-38.559329</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10585,10 +10625,10 @@
         <v>273</v>
       </c>
       <c r="V48" s="5" t="n">
-        <v>-3.7644943</v>
+        <v>-3.764802</v>
       </c>
       <c r="W48" s="5" t="n">
-        <v>-38.5878033</v>
+        <v>-38.588194</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10646,10 +10686,10 @@
         <v>278</v>
       </c>
       <c r="V49" s="5" t="n">
-        <v>-3.756179</v>
+        <v>-3.756168</v>
       </c>
       <c r="W49" s="5" t="n">
-        <v>-38.5023464</v>
+        <v>-38.50234</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10705,10 +10745,10 @@
         <v>283</v>
       </c>
       <c r="V50" s="5" t="n">
-        <v>-3.7252764</v>
+        <v>-3.725691</v>
       </c>
       <c r="W50" s="5" t="n">
-        <v>-38.4665505</v>
+        <v>-38.466675</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10765,8 +10805,12 @@
       <c r="U51" s="5" t="s">
         <v>288</v>
       </c>
-      <c r="V51" s="5"/>
-      <c r="W51" s="5"/>
+      <c r="V51" s="5" t="n">
+        <v>-3.729464</v>
+      </c>
+      <c r="W51" s="5" t="n">
+        <v>-38.570643</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5" t="s">
@@ -10821,10 +10865,10 @@
         <v>293</v>
       </c>
       <c r="V52" s="5" t="n">
-        <v>-3.7561705</v>
+        <v>-3.755865</v>
       </c>
       <c r="W52" s="5" t="n">
-        <v>-38.5921377</v>
+        <v>-38.592013</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10880,10 +10924,10 @@
         <v>298</v>
       </c>
       <c r="V53" s="5" t="n">
-        <v>-3.74495</v>
+        <v>-3.744884</v>
       </c>
       <c r="W53" s="5" t="n">
-        <v>-38.4967378</v>
+        <v>-38.496875</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10939,10 +10983,10 @@
         <v>303</v>
       </c>
       <c r="V54" s="5" t="n">
-        <v>-3.7891398</v>
+        <v>-3.789179</v>
       </c>
       <c r="W54" s="5" t="n">
-        <v>-38.5978866</v>
+        <v>-38.597875</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10998,10 +11042,10 @@
         <v>307</v>
       </c>
       <c r="V55" s="5" t="n">
-        <v>-3.8275696</v>
+        <v>-3.829086</v>
       </c>
       <c r="W55" s="5" t="n">
-        <v>-38.5594362</v>
+        <v>-38.55693</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11061,10 +11105,10 @@
         <v>312</v>
       </c>
       <c r="V56" s="5" t="n">
-        <v>-3.7559388</v>
+        <v>-3.755883</v>
       </c>
       <c r="W56" s="5" t="n">
-        <v>-38.5839212</v>
+        <v>-38.583951</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11120,10 +11164,10 @@
         <v>316</v>
       </c>
       <c r="V57" s="5" t="n">
-        <v>-3.7327023</v>
+        <v>-3.732608</v>
       </c>
       <c r="W57" s="5" t="n">
-        <v>-38.5578905</v>
+        <v>-38.557913</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11181,10 +11225,10 @@
         <v>320</v>
       </c>
       <c r="V58" s="5" t="n">
-        <v>-3.7063714</v>
+        <v>-3.706478</v>
       </c>
       <c r="W58" s="5" t="n">
-        <v>-38.5852771</v>
+        <v>-38.585312</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11248,10 +11292,10 @@
         <v>325</v>
       </c>
       <c r="V59" s="5" t="n">
-        <v>-3.8281785</v>
+        <v>-3.82824</v>
       </c>
       <c r="W59" s="5" t="n">
-        <v>-38.5305368</v>
+        <v>-38.530484</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11309,10 +11353,10 @@
         <v>331</v>
       </c>
       <c r="V60" s="5" t="n">
-        <v>-3.8524034</v>
+        <v>-3.851678</v>
       </c>
       <c r="W60" s="5" t="n">
-        <v>-38.4994765</v>
+        <v>-38.502448</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11369,8 +11413,12 @@
       <c r="U61" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="V61" s="5"/>
-      <c r="W61" s="5"/>
+      <c r="V61" s="5" t="n">
+        <v>-3.796236</v>
+      </c>
+      <c r="W61" s="5" t="n">
+        <v>-38.613854</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5" t="s">
@@ -11427,10 +11475,10 @@
         <v>339</v>
       </c>
       <c r="V62" s="5" t="n">
-        <v>-3.7772557</v>
+        <v>-3.77723</v>
       </c>
       <c r="W62" s="5" t="n">
-        <v>-38.6173674</v>
+        <v>-38.617417</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11488,10 +11536,10 @@
         <v>344</v>
       </c>
       <c r="V63" s="5" t="n">
-        <v>-3.8256771</v>
+        <v>-3.827032</v>
       </c>
       <c r="W63" s="5" t="n">
-        <v>-38.4573864</v>
+        <v>-38.457103</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11549,10 +11597,10 @@
         <v>348</v>
       </c>
       <c r="V64" s="5" t="n">
-        <v>-3.8041678</v>
+        <v>-3.79287</v>
       </c>
       <c r="W64" s="5" t="n">
-        <v>-38.5221623</v>
+        <v>-38.518283</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11610,10 +11658,10 @@
         <v>352</v>
       </c>
       <c r="V65" s="5" t="n">
-        <v>-3.8145705</v>
+        <v>-3.81317</v>
       </c>
       <c r="W65" s="5" t="n">
-        <v>-38.5391701</v>
+        <v>-38.537945</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11671,10 +11719,10 @@
         <v>357</v>
       </c>
       <c r="V66" s="5" t="n">
-        <v>-3.8512946</v>
+        <v>-3.85132</v>
       </c>
       <c r="W66" s="5" t="n">
-        <v>-38.524321</v>
+        <v>-38.524344</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11732,10 +11780,10 @@
         <v>361</v>
       </c>
       <c r="V67" s="5" t="n">
-        <v>-3.827182</v>
+        <v>-3.827022</v>
       </c>
       <c r="W67" s="5" t="n">
-        <v>-38.4639405</v>
+        <v>-38.463638</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11793,10 +11841,10 @@
         <v>365</v>
       </c>
       <c r="V68" s="5" t="n">
-        <v>-3.8300894</v>
+        <v>-3.829569</v>
       </c>
       <c r="W68" s="5" t="n">
-        <v>-38.5577124</v>
+        <v>-38.557183</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11854,10 +11902,10 @@
         <v>370</v>
       </c>
       <c r="V69" s="5" t="n">
-        <v>-3.8085486</v>
+        <v>-3.806945</v>
       </c>
       <c r="W69" s="5" t="n">
-        <v>-38.6005947</v>
+        <v>-38.602655</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11915,10 +11963,10 @@
         <v>375</v>
       </c>
       <c r="V70" s="5" t="n">
-        <v>-3.8317425</v>
+        <v>-3.831655</v>
       </c>
       <c r="W70" s="5" t="n">
-        <v>-38.5214838</v>
+        <v>-38.518013</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -11976,10 +12024,10 @@
         <v>380</v>
       </c>
       <c r="V71" s="5" t="n">
-        <v>-3.8475604</v>
+        <v>-3.847559</v>
       </c>
       <c r="W71" s="5" t="n">
-        <v>-38.4812029</v>
+        <v>-38.481198</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12039,10 +12087,10 @@
         <v>386</v>
       </c>
       <c r="V72" s="5" t="n">
-        <v>-3.7514045</v>
+        <v>-3.750385</v>
       </c>
       <c r="W72" s="5" t="n">
-        <v>-38.5626401</v>
+        <v>-38.562608</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12100,10 +12148,10 @@
         <v>391</v>
       </c>
       <c r="V73" s="5" t="n">
-        <v>-3.7817431</v>
+        <v>-3.779827</v>
       </c>
       <c r="W73" s="5" t="n">
-        <v>-38.5822335</v>
+        <v>-38.589604</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12163,10 +12211,10 @@
         <v>396</v>
       </c>
       <c r="V74" s="5" t="n">
-        <v>-3.8179058</v>
+        <v>-3.817691</v>
       </c>
       <c r="W74" s="5" t="n">
-        <v>-38.4759913</v>
+        <v>-38.475974</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12226,10 +12274,10 @@
         <v>400</v>
       </c>
       <c r="V75" s="5" t="n">
-        <v>-3.7846627</v>
+        <v>-3.784616</v>
       </c>
       <c r="W75" s="5" t="n">
-        <v>-38.6267844</v>
+        <v>-38.626701</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12293,10 +12341,10 @@
         <v>405</v>
       </c>
       <c r="V76" s="5" t="n">
-        <v>-3.7647783</v>
+        <v>-3.764841</v>
       </c>
       <c r="W76" s="5" t="n">
-        <v>-38.5791536</v>
+        <v>-38.579225</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12354,10 +12402,10 @@
         <v>45</v>
       </c>
       <c r="V77" s="5" t="n">
-        <v>-3.7133858</v>
+        <v>-3.713077</v>
       </c>
       <c r="W77" s="5" t="n">
-        <v>-38.5544973</v>
+        <v>-38.555037</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12415,10 +12463,10 @@
         <v>411</v>
       </c>
       <c r="V78" s="5" t="n">
-        <v>-3.7771026</v>
+        <v>-3.777103</v>
       </c>
       <c r="W78" s="5" t="n">
-        <v>-38.6018164</v>
+        <v>-38.601816</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12482,10 +12530,10 @@
         <v>416</v>
       </c>
       <c r="V79" s="5" t="n">
-        <v>-3.7222901</v>
+        <v>-3.722184</v>
       </c>
       <c r="W79" s="5" t="n">
-        <v>-38.5575345</v>
+        <v>-38.557389</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12540,8 +12588,12 @@
       <c r="U80" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="V80" s="5"/>
-      <c r="W80" s="5"/>
+      <c r="V80" s="5" t="n">
+        <v>-3.799207</v>
+      </c>
+      <c r="W80" s="5" t="n">
+        <v>-38.545983</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="5" t="s">
@@ -12604,10 +12656,10 @@
         <v>424</v>
       </c>
       <c r="V81" s="5" t="n">
-        <v>-3.8419851</v>
+        <v>-3.841856</v>
       </c>
       <c r="W81" s="5" t="n">
-        <v>-38.4867544</v>
+        <v>-38.486591</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12663,10 +12715,10 @@
         <v>428</v>
       </c>
       <c r="V82" s="5" t="n">
-        <v>-3.8160315</v>
+        <v>-3.816031</v>
       </c>
       <c r="W82" s="5" t="n">
-        <v>-38.4767834</v>
+        <v>-38.476783</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12722,10 +12774,10 @@
         <v>432</v>
       </c>
       <c r="V83" s="5" t="n">
-        <v>-3.7773281</v>
+        <v>-3.777328</v>
       </c>
       <c r="W83" s="5" t="n">
-        <v>-38.6011773</v>
+        <v>-38.601177</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12789,10 +12841,10 @@
         <v>438</v>
       </c>
       <c r="V84" s="5" t="n">
-        <v>-3.7614195</v>
+        <v>-3.761269</v>
       </c>
       <c r="W84" s="5" t="n">
-        <v>-38.5138058</v>
+        <v>-38.513709</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12854,10 +12906,10 @@
         <v>443</v>
       </c>
       <c r="V85" s="5" t="n">
-        <v>-3.7823748</v>
+        <v>-3.782364</v>
       </c>
       <c r="W85" s="5" t="n">
-        <v>-38.5614753</v>
+        <v>-38.561523</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12921,10 +12973,10 @@
         <v>449</v>
       </c>
       <c r="V86" s="5" t="n">
-        <v>-3.7253597</v>
+        <v>-3.72536</v>
       </c>
       <c r="W86" s="5" t="n">
-        <v>-38.5843895</v>
+        <v>-38.584389</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -12980,10 +13032,10 @@
         <v>453</v>
       </c>
       <c r="V87" s="5" t="n">
-        <v>-3.8480534</v>
+        <v>-3.846545</v>
       </c>
       <c r="W87" s="5" t="n">
-        <v>-38.5229069</v>
+        <v>-38.522731</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13039,10 +13091,10 @@
         <v>458</v>
       </c>
       <c r="V88" s="5" t="n">
-        <v>-3.7197244</v>
+        <v>-3.719624</v>
       </c>
       <c r="W88" s="5" t="n">
-        <v>-38.5155305</v>
+        <v>-38.515523</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13098,10 +13150,10 @@
         <v>462</v>
       </c>
       <c r="V89" s="5" t="n">
-        <v>-3.7864956</v>
+        <v>-3.786493</v>
       </c>
       <c r="W89" s="5" t="n">
-        <v>-38.6038997</v>
+        <v>-38.603878</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13157,10 +13209,10 @@
         <v>466</v>
       </c>
       <c r="V90" s="5" t="n">
-        <v>-3.7887918</v>
+        <v>-3.788126</v>
       </c>
       <c r="W90" s="5" t="n">
-        <v>-38.6104083</v>
+        <v>-38.609522</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13216,10 +13268,10 @@
         <v>470</v>
       </c>
       <c r="V91" s="5" t="n">
-        <v>-3.7817791</v>
+        <v>-3.78178</v>
       </c>
       <c r="W91" s="5" t="n">
-        <v>-38.6025479</v>
+        <v>-38.602544</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13283,10 +13335,10 @@
         <v>476</v>
       </c>
       <c r="V92" s="5" t="n">
-        <v>-3.7196197</v>
+        <v>-3.71966</v>
       </c>
       <c r="W92" s="5" t="n">
-        <v>-38.5350944</v>
+        <v>-38.53512</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13342,10 +13394,10 @@
         <v>480</v>
       </c>
       <c r="V93" s="5" t="n">
-        <v>-3.7773045</v>
+        <v>-3.77712</v>
       </c>
       <c r="W93" s="5" t="n">
-        <v>-38.6032321</v>
+        <v>-38.601468</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13401,10 +13453,10 @@
         <v>485</v>
       </c>
       <c r="V94" s="5" t="n">
-        <v>-3.8287534</v>
+        <v>-3.830201</v>
       </c>
       <c r="W94" s="5" t="n">
-        <v>-38.6009022</v>
+        <v>-38.598411</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13460,10 +13512,10 @@
         <v>489</v>
       </c>
       <c r="V95" s="5" t="n">
-        <v>-3.827559</v>
+        <v>-3.830004</v>
       </c>
       <c r="W95" s="5" t="n">
-        <v>-38.5900057</v>
+        <v>-38.591145</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13527,10 +13579,10 @@
         <v>495</v>
       </c>
       <c r="V96" s="5" t="n">
-        <v>-3.7386691</v>
+        <v>-3.739251</v>
       </c>
       <c r="W96" s="5" t="n">
-        <v>-38.5799766</v>
+        <v>-38.579972</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13588,10 +13640,10 @@
         <v>499</v>
       </c>
       <c r="V97" s="5" t="n">
-        <v>-3.7897295</v>
+        <v>-3.789359</v>
       </c>
       <c r="W97" s="5" t="n">
-        <v>-38.4485917</v>
+        <v>-38.448965</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13649,10 +13701,10 @@
         <v>503</v>
       </c>
       <c r="V98" s="5" t="n">
-        <v>-3.7005049</v>
+        <v>-3.700712</v>
       </c>
       <c r="W98" s="5" t="n">
-        <v>-38.5856701</v>
+        <v>-38.585599</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13710,10 +13762,10 @@
         <v>508</v>
       </c>
       <c r="V99" s="5" t="n">
-        <v>-3.7221681</v>
+        <v>-3.72198</v>
       </c>
       <c r="W99" s="5" t="n">
-        <v>-38.5909022</v>
+        <v>-38.591448</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13777,10 +13829,10 @@
         <v>513</v>
       </c>
       <c r="V100" s="5" t="n">
-        <v>-3.8038855</v>
+        <v>-3.803907</v>
       </c>
       <c r="W100" s="5" t="n">
-        <v>-38.5855778</v>
+        <v>-38.5856</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13844,10 +13896,10 @@
         <v>518</v>
       </c>
       <c r="V101" s="5" t="n">
-        <v>-3.7274238</v>
+        <v>-3.727319</v>
       </c>
       <c r="W101" s="5" t="n">
-        <v>-38.4786105</v>
+        <v>-38.478525</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -13908,8 +13960,12 @@
       <c r="U102" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="V102" s="5"/>
-      <c r="W102" s="5"/>
+      <c r="V102" s="5" t="n">
+        <v>-3.807902</v>
+      </c>
+      <c r="W102" s="5" t="n">
+        <v>-38.617252</v>
+      </c>
     </row>
     <row r="103" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="5" t="s">
@@ -13969,8 +14025,12 @@
       <c r="U103" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="V103" s="5"/>
-      <c r="W103" s="5"/>
+      <c r="V103" s="5" t="n">
+        <v>-3.839015</v>
+      </c>
+      <c r="W103" s="5" t="n">
+        <v>-38.552066</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="5" t="s">
@@ -14030,8 +14090,12 @@
       <c r="U104" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="V104" s="5"/>
-      <c r="W104" s="5"/>
+      <c r="V104" s="5" t="n">
+        <v>-3.804689</v>
+      </c>
+      <c r="W104" s="5" t="n">
+        <v>-38.54841</v>
+      </c>
     </row>
     <row r="105" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="5" t="s">
@@ -14092,10 +14156,10 @@
         <v>536</v>
       </c>
       <c r="V105" s="5" t="n">
-        <v>-3.8386356</v>
+        <v>-3.838986</v>
       </c>
       <c r="W105" s="5" t="n">
-        <v>-38.5233375</v>
+        <v>-38.523928</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14157,10 +14221,10 @@
         <v>541</v>
       </c>
       <c r="V106" s="5" t="n">
-        <v>-3.8498129</v>
+        <v>-3.852628</v>
       </c>
       <c r="W106" s="5" t="n">
-        <v>-38.5229252</v>
+        <v>-38.524126</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14218,10 +14282,10 @@
         <v>545</v>
       </c>
       <c r="V107" s="5" t="n">
-        <v>-3.8393439</v>
+        <v>-3.839344</v>
       </c>
       <c r="W107" s="5" t="n">
-        <v>-38.5275683</v>
+        <v>-38.527568</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14283,10 +14347,10 @@
         <v>549</v>
       </c>
       <c r="V108" s="5" t="n">
-        <v>-3.8248032</v>
+        <v>-3.823657</v>
       </c>
       <c r="W108" s="5" t="n">
-        <v>-38.4649469</v>
+        <v>-38.46499</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14342,10 +14406,10 @@
         <v>554</v>
       </c>
       <c r="V109" s="5" t="n">
-        <v>-3.7494799</v>
+        <v>-3.749655</v>
       </c>
       <c r="W109" s="5" t="n">
-        <v>-38.5924455</v>
+        <v>-38.592513</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14401,10 +14465,10 @@
         <v>558</v>
       </c>
       <c r="V110" s="5" t="n">
-        <v>-3.7318937</v>
+        <v>-3.731889</v>
       </c>
       <c r="W110" s="5" t="n">
-        <v>-38.5039111</v>
+        <v>-38.503914</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14460,10 +14524,10 @@
         <v>563</v>
       </c>
       <c r="V111" s="5" t="n">
-        <v>-3.7508984</v>
+        <v>-3.750898</v>
       </c>
       <c r="W111" s="5" t="n">
-        <v>-38.5378287</v>
+        <v>-38.537831</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14519,10 +14583,10 @@
         <v>570</v>
       </c>
       <c r="V112" s="5" t="n">
-        <v>-3.7216128</v>
+        <v>-3.721494</v>
       </c>
       <c r="W112" s="5" t="n">
-        <v>-38.5353713</v>
+        <v>-38.535374</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14578,10 +14642,10 @@
         <v>574</v>
       </c>
       <c r="V113" s="5" t="n">
-        <v>-3.70654</v>
+        <v>-3.706547</v>
       </c>
       <c r="W113" s="5" t="n">
-        <v>-38.5706292</v>
+        <v>-38.570631</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14639,10 +14703,10 @@
         <v>578</v>
       </c>
       <c r="V114" s="5" t="n">
-        <v>-3.8587207</v>
+        <v>-3.858964</v>
       </c>
       <c r="W114" s="5" t="n">
-        <v>-38.4927741</v>
+        <v>-38.493364</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14708,10 +14772,10 @@
         <v>499</v>
       </c>
       <c r="V115" s="5" t="n">
-        <v>-3.7897295</v>
+        <v>-3.789507</v>
       </c>
       <c r="W115" s="5" t="n">
-        <v>-38.4485917</v>
+        <v>-38.448727</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14774,8 +14838,12 @@
       <c r="U116" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="V116" s="5"/>
-      <c r="W116" s="5"/>
+      <c r="V116" s="5" t="n">
+        <v>-3.711368</v>
+      </c>
+      <c r="W116" s="5" t="n">
+        <v>-38.600089</v>
+      </c>
     </row>
     <row r="117" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="5" t="s">
@@ -14839,8 +14907,12 @@
       <c r="U117" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="V117" s="5"/>
-      <c r="W117" s="5"/>
+      <c r="V117" s="5" t="n">
+        <v>-3.84591</v>
+      </c>
+      <c r="W117" s="5" t="n">
+        <v>-38.504775</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="5" t="s">
@@ -14905,10 +14977,10 @@
         <v>598</v>
       </c>
       <c r="V118" s="5" t="n">
-        <v>-3.7449655</v>
+        <v>-3.745061</v>
       </c>
       <c r="W118" s="5" t="n">
-        <v>-38.454796</v>
+        <v>-38.454743</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14972,10 +15044,10 @@
         <v>603</v>
       </c>
       <c r="V119" s="5" t="n">
-        <v>-3.7967317</v>
+        <v>-3.796508</v>
       </c>
       <c r="W119" s="5" t="n">
-        <v>-38.6139453</v>
+        <v>-38.613564</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15031,10 +15103,10 @@
         <v>607</v>
       </c>
       <c r="V120" s="5" t="n">
-        <v>-3.7319579</v>
+        <v>-3.731983</v>
       </c>
       <c r="W120" s="5" t="n">
-        <v>-38.5226557</v>
+        <v>-38.522634</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15090,10 +15162,10 @@
         <v>611</v>
       </c>
       <c r="V121" s="5" t="n">
-        <v>-3.7067955</v>
+        <v>-3.706812</v>
       </c>
       <c r="W121" s="5" t="n">
-        <v>-38.5745129</v>
+        <v>-38.574557</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15149,10 +15221,10 @@
         <v>615</v>
       </c>
       <c r="V122" s="5" t="n">
-        <v>-3.7989056</v>
+        <v>-3.79926</v>
       </c>
       <c r="W122" s="5" t="n">
-        <v>-38.5626128</v>
+        <v>-38.562999</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15210,10 +15282,10 @@
         <v>620</v>
       </c>
       <c r="V123" s="5" t="n">
-        <v>-3.8253146</v>
+        <v>-3.826084</v>
       </c>
       <c r="W123" s="5" t="n">
-        <v>-38.4578513</v>
+        <v>-38.457728</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15271,10 +15343,10 @@
         <v>625</v>
       </c>
       <c r="V124" s="5" t="n">
-        <v>-3.7442892</v>
+        <v>-3.74421</v>
       </c>
       <c r="W124" s="5" t="n">
-        <v>-38.4692768</v>
+        <v>-38.468979</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15329,8 +15401,12 @@
       <c r="U125" s="5" t="s">
         <v>629</v>
       </c>
-      <c r="V125" s="5"/>
-      <c r="W125" s="5"/>
+      <c r="V125" s="5" t="n">
+        <v>-3.813362</v>
+      </c>
+      <c r="W125" s="5" t="n">
+        <v>-38.580534</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="5" t="s">
@@ -15387,10 +15463,10 @@
         <v>633</v>
       </c>
       <c r="V126" s="5" t="n">
-        <v>-3.7834593</v>
+        <v>-3.78347</v>
       </c>
       <c r="W126" s="5" t="n">
-        <v>-38.5900961</v>
+        <v>-38.590083</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15446,10 +15522,10 @@
         <v>637</v>
       </c>
       <c r="V127" s="5" t="n">
-        <v>-3.8573115</v>
+        <v>-3.857772</v>
       </c>
       <c r="W127" s="5" t="n">
-        <v>-38.5169121</v>
+        <v>-38.516908</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15505,10 +15581,10 @@
         <v>641</v>
       </c>
       <c r="V128" s="5" t="n">
-        <v>-3.7739275</v>
+        <v>-3.773738</v>
       </c>
       <c r="W128" s="5" t="n">
-        <v>-38.5842821</v>
+        <v>-38.584098</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15564,10 +15640,10 @@
         <v>646</v>
       </c>
       <c r="V129" s="5" t="n">
-        <v>-3.7712235</v>
+        <v>-3.770991</v>
       </c>
       <c r="W129" s="5" t="n">
-        <v>-38.5157565</v>
+        <v>-38.515955</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15622,8 +15698,12 @@
       <c r="U130" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="V130" s="5"/>
-      <c r="W130" s="5"/>
+      <c r="V130" s="5" t="n">
+        <v>-3.77634</v>
+      </c>
+      <c r="W130" s="5" t="n">
+        <v>-38.594403</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="5" t="s">
@@ -15680,10 +15760,10 @@
         <v>655</v>
       </c>
       <c r="V131" s="5" t="n">
-        <v>-3.7560489</v>
+        <v>-3.756023</v>
       </c>
       <c r="W131" s="5" t="n">
-        <v>-38.6032216</v>
+        <v>-38.60325</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15739,10 +15819,10 @@
         <v>659</v>
       </c>
       <c r="V132" s="5" t="n">
-        <v>-3.8067581</v>
+        <v>-3.806809</v>
       </c>
       <c r="W132" s="5" t="n">
-        <v>-38.5931277</v>
+        <v>-38.593229</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15798,10 +15878,10 @@
         <v>664</v>
       </c>
       <c r="V133" s="5" t="n">
-        <v>-3.7670006</v>
+        <v>-3.768325</v>
       </c>
       <c r="W133" s="5" t="n">
-        <v>-38.5992936</v>
+        <v>-38.59913</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15857,10 +15937,10 @@
         <v>668</v>
       </c>
       <c r="V134" s="5" t="n">
-        <v>-3.7695316</v>
+        <v>-3.76816</v>
       </c>
       <c r="W134" s="5" t="n">
-        <v>-38.5973424</v>
+        <v>-38.596758</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15916,10 +15996,10 @@
         <v>672</v>
       </c>
       <c r="V135" s="5" t="n">
-        <v>-3.8382207</v>
+        <v>-3.83807</v>
       </c>
       <c r="W135" s="5" t="n">
-        <v>-38.5787703</v>
+        <v>-38.580604</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -15976,8 +16056,12 @@
       <c r="U136" s="5" t="s">
         <v>676</v>
       </c>
-      <c r="V136" s="5"/>
-      <c r="W136" s="5"/>
+      <c r="V136" s="5" t="n">
+        <v>-3.800117</v>
+      </c>
+      <c r="W136" s="5" t="n">
+        <v>-38.540671</v>
+      </c>
     </row>
     <row r="137" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="5" t="s">
@@ -16032,10 +16116,10 @@
         <v>680</v>
       </c>
       <c r="V137" s="5" t="n">
-        <v>-3.7264211</v>
+        <v>-3.726526</v>
       </c>
       <c r="W137" s="5" t="n">
-        <v>-38.4770514</v>
+        <v>-38.47699</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16091,10 +16175,10 @@
         <v>685</v>
       </c>
       <c r="V138" s="5" t="n">
-        <v>-3.7152793</v>
+        <v>-3.715282</v>
       </c>
       <c r="W138" s="5" t="n">
-        <v>-38.5621025</v>
+        <v>-38.561998</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16151,8 +16235,12 @@
       <c r="U139" s="5" t="s">
         <v>689</v>
       </c>
-      <c r="V139" s="5"/>
-      <c r="W139" s="5"/>
+      <c r="V139" s="5" t="n">
+        <v>-3.73074</v>
+      </c>
+      <c r="W139" s="5" t="n">
+        <v>-38.58093</v>
+      </c>
     </row>
     <row r="140" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="5" t="s">
@@ -16207,10 +16295,10 @@
         <v>693</v>
       </c>
       <c r="V140" s="5" t="n">
-        <v>-3.7061881</v>
+        <v>-3.706174</v>
       </c>
       <c r="W140" s="5" t="n">
-        <v>-38.5595138</v>
+        <v>-38.559514</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16274,10 +16362,10 @@
         <v>699</v>
       </c>
       <c r="V141" s="5" t="n">
-        <v>-3.7394913</v>
+        <v>-3.739843</v>
       </c>
       <c r="W141" s="5" t="n">
-        <v>-38.5816643</v>
+        <v>-38.581581</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16333,10 +16421,10 @@
         <v>704</v>
       </c>
       <c r="V142" s="5" t="n">
-        <v>-3.7907287</v>
+        <v>-3.790729</v>
       </c>
       <c r="W142" s="5" t="n">
-        <v>-38.5978208</v>
+        <v>-38.597821</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16392,10 +16480,10 @@
         <v>709</v>
       </c>
       <c r="V143" s="5" t="n">
-        <v>-3.7681474</v>
+        <v>-3.768163</v>
       </c>
       <c r="W143" s="5" t="n">
-        <v>-38.5777038</v>
+        <v>-38.577678</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16451,10 +16539,10 @@
         <v>713</v>
       </c>
       <c r="V144" s="5" t="n">
-        <v>-3.7049054</v>
+        <v>-3.70494</v>
       </c>
       <c r="W144" s="5" t="n">
-        <v>-38.576508</v>
+        <v>-38.576493</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16510,10 +16598,10 @@
         <v>717</v>
       </c>
       <c r="V145" s="5" t="n">
-        <v>-3.7218042</v>
+        <v>-3.721614</v>
       </c>
       <c r="W145" s="5" t="n">
-        <v>-38.5912409</v>
+        <v>-38.591362</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16577,10 +16665,10 @@
         <v>723</v>
       </c>
       <c r="V146" s="5" t="n">
-        <v>-3.8150967</v>
+        <v>-3.815015</v>
       </c>
       <c r="W146" s="5" t="n">
-        <v>-38.5031065</v>
+        <v>-38.503274</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16644,10 +16732,10 @@
         <v>729</v>
       </c>
       <c r="V147" s="5" t="n">
-        <v>-3.7752196</v>
+        <v>-3.774401</v>
       </c>
       <c r="W147" s="5" t="n">
-        <v>-38.6170375</v>
+        <v>-38.618447</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16705,10 +16793,10 @@
         <v>734</v>
       </c>
       <c r="V148" s="5" t="n">
-        <v>-3.7137948</v>
+        <v>-3.71398</v>
       </c>
       <c r="W148" s="5" t="n">
-        <v>-38.6020376</v>
+        <v>-38.600774</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16764,10 +16852,10 @@
         <v>738</v>
       </c>
       <c r="V149" s="5" t="n">
-        <v>-3.8110252</v>
+        <v>-3.811069</v>
       </c>
       <c r="W149" s="5" t="n">
-        <v>-38.5845911</v>
+        <v>-38.584562</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16826,7 +16914,7 @@
         <v>-3.801766</v>
       </c>
       <c r="W150" s="5" t="n">
-        <v>-38.5986645</v>
+        <v>-38.598665</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16884,10 +16972,10 @@
         <v>747</v>
       </c>
       <c r="V151" s="5" t="n">
-        <v>-3.7090278</v>
+        <v>-3.708211</v>
       </c>
       <c r="W151" s="5" t="n">
-        <v>-38.5861466</v>
+        <v>-38.58384</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16951,10 +17039,10 @@
         <v>751</v>
       </c>
       <c r="V152" s="5" t="n">
-        <v>-3.7714484</v>
+        <v>-3.772159</v>
       </c>
       <c r="W152" s="5" t="n">
-        <v>-38.6037827</v>
+        <v>-38.602729</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17010,10 +17098,10 @@
         <v>570</v>
       </c>
       <c r="V153" s="5" t="n">
-        <v>-3.7216128</v>
+        <v>-3.721613</v>
       </c>
       <c r="W153" s="5" t="n">
-        <v>-38.5353713</v>
+        <v>-38.535371</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17069,10 +17157,10 @@
         <v>757</v>
       </c>
       <c r="V154" s="5" t="n">
-        <v>-3.7294021</v>
+        <v>-3.729379</v>
       </c>
       <c r="W154" s="5" t="n">
-        <v>-38.5830907</v>
+        <v>-38.583388</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17136,10 +17224,10 @@
         <v>761</v>
       </c>
       <c r="V155" s="5" t="n">
-        <v>-3.7660252</v>
+        <v>-3.7649</v>
       </c>
       <c r="W155" s="5" t="n">
-        <v>-38.6093611</v>
+        <v>-38.608717</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17195,10 +17283,10 @@
         <v>766</v>
       </c>
       <c r="V156" s="5" t="n">
-        <v>-3.8845589</v>
+        <v>-3.879807</v>
       </c>
       <c r="W156" s="5" t="n">
-        <v>-38.525222</v>
+        <v>-38.530262</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17254,10 +17342,10 @@
         <v>770</v>
       </c>
       <c r="V157" s="5" t="n">
-        <v>-3.7780124</v>
+        <v>-3.778012</v>
       </c>
       <c r="W157" s="5" t="n">
-        <v>-38.4772262</v>
+        <v>-38.477226</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17318,8 +17406,12 @@
       <c r="U158" s="5" t="s">
         <v>775</v>
       </c>
-      <c r="V158" s="5"/>
-      <c r="W158" s="5"/>
+      <c r="V158" s="5" t="n">
+        <v>-3.838618</v>
+      </c>
+      <c r="W158" s="5" t="n">
+        <v>-38.490512</v>
+      </c>
     </row>
     <row r="159" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="5" t="s">
@@ -17374,10 +17466,10 @@
         <v>779</v>
       </c>
       <c r="V159" s="5" t="n">
-        <v>-3.8209629</v>
+        <v>-3.814289</v>
       </c>
       <c r="W159" s="5" t="n">
-        <v>-38.5838233</v>
+        <v>-38.578645</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17433,10 +17525,10 @@
         <v>784</v>
       </c>
       <c r="V160" s="5" t="n">
-        <v>-3.7448694</v>
+        <v>-3.752343</v>
       </c>
       <c r="W160" s="5" t="n">
-        <v>-38.5848612</v>
+        <v>-38.582608</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17491,8 +17583,12 @@
       <c r="U161" s="5" t="s">
         <v>789</v>
       </c>
-      <c r="V161" s="5"/>
-      <c r="W161" s="5"/>
+      <c r="V161" s="5" t="n">
+        <v>-3.826412</v>
+      </c>
+      <c r="W161" s="5" t="n">
+        <v>-38.516572</v>
+      </c>
     </row>
     <row r="162" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="5" t="s">
@@ -17547,10 +17643,10 @@
         <v>794</v>
       </c>
       <c r="V162" s="5" t="n">
-        <v>-3.718072</v>
+        <v>-3.717616</v>
       </c>
       <c r="W162" s="5" t="n">
-        <v>-38.4653616</v>
+        <v>-38.465256</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17606,10 +17702,10 @@
         <v>798</v>
       </c>
       <c r="V163" s="5" t="n">
-        <v>-3.8313686</v>
+        <v>-3.830863</v>
       </c>
       <c r="W163" s="5" t="n">
-        <v>-38.5979663</v>
+        <v>-38.597926</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17675,10 +17771,10 @@
         <v>804</v>
       </c>
       <c r="V164" s="5" t="n">
-        <v>-3.7484215</v>
+        <v>-3.74843</v>
       </c>
       <c r="W164" s="5" t="n">
-        <v>-38.5573763</v>
+        <v>-38.557375</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17734,10 +17830,10 @@
         <v>809</v>
       </c>
       <c r="V165" s="5" t="n">
-        <v>-3.7316911</v>
+        <v>-3.731618</v>
       </c>
       <c r="W165" s="5" t="n">
-        <v>-38.5020483</v>
+        <v>-38.502008</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17795,10 +17891,10 @@
         <v>813</v>
       </c>
       <c r="V166" s="5" t="n">
-        <v>-3.7219669</v>
+        <v>-3.722202</v>
       </c>
       <c r="W166" s="5" t="n">
-        <v>-38.4674257</v>
+        <v>-38.471393</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17862,10 +17958,10 @@
         <v>818</v>
       </c>
       <c r="V167" s="5" t="n">
-        <v>-3.7537765</v>
+        <v>-3.753588</v>
       </c>
       <c r="W167" s="5" t="n">
-        <v>-38.601364</v>
+        <v>-38.601247</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17929,10 +18025,10 @@
         <v>824</v>
       </c>
       <c r="V168" s="5" t="n">
-        <v>-3.8044632</v>
+        <v>-3.805869</v>
       </c>
       <c r="W168" s="5" t="n">
-        <v>-38.6213706</v>
+        <v>-38.622742</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -17996,10 +18092,10 @@
         <v>829</v>
       </c>
       <c r="V169" s="5" t="n">
-        <v>-3.7508913</v>
+        <v>-3.752581</v>
       </c>
       <c r="W169" s="5" t="n">
-        <v>-38.5418172</v>
+        <v>-38.53864</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18063,10 +18159,10 @@
         <v>834</v>
       </c>
       <c r="V170" s="5" t="n">
-        <v>-3.8389444</v>
+        <v>-3.838986</v>
       </c>
       <c r="W170" s="5" t="n">
-        <v>-38.5279732</v>
+        <v>-38.527345</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18121,8 +18217,12 @@
       <c r="U171" s="5" t="s">
         <v>838</v>
       </c>
-      <c r="V171" s="5"/>
-      <c r="W171" s="5"/>
+      <c r="V171" s="5" t="n">
+        <v>-3.749716</v>
+      </c>
+      <c r="W171" s="5" t="n">
+        <v>-38.566626</v>
+      </c>
     </row>
     <row r="172" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="5" t="s">
@@ -18176,8 +18276,12 @@
       <c r="U172" s="5" t="s">
         <v>842</v>
       </c>
-      <c r="V172" s="5"/>
-      <c r="W172" s="5"/>
+      <c r="V172" s="5" t="n">
+        <v>-3.707966</v>
+      </c>
+      <c r="W172" s="5" t="n">
+        <v>-38.563185</v>
+      </c>
     </row>
     <row r="173" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="5" t="s">
@@ -18233,8 +18337,12 @@
       <c r="U173" s="5" t="s">
         <v>846</v>
       </c>
-      <c r="V173" s="5"/>
-      <c r="W173" s="5"/>
+      <c r="V173" s="5" t="n">
+        <v>-3.807196</v>
+      </c>
+      <c r="W173" s="5" t="n">
+        <v>-38.601131</v>
+      </c>
     </row>
     <row r="174" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="5" t="s">
@@ -18289,10 +18397,10 @@
         <v>850</v>
       </c>
       <c r="V174" s="5" t="n">
-        <v>-3.7545894</v>
+        <v>-3.754669</v>
       </c>
       <c r="W174" s="5" t="n">
-        <v>-38.5452298</v>
+        <v>-38.545179</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18356,10 +18464,10 @@
         <v>855</v>
       </c>
       <c r="V175" s="5" t="n">
-        <v>-3.7731497</v>
+        <v>-3.77301</v>
       </c>
       <c r="W175" s="5" t="n">
-        <v>-38.4560858</v>
+        <v>-38.455401</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18418,7 +18526,7 @@
         <v>-3.77338</v>
       </c>
       <c r="W176" s="5" t="n">
-        <v>-38.4915738</v>
+        <v>-38.491574</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18474,10 +18582,10 @@
         <v>864</v>
       </c>
       <c r="V177" s="5" t="n">
-        <v>-3.722348</v>
+        <v>-3.72233</v>
       </c>
       <c r="W177" s="5" t="n">
-        <v>-38.4756663</v>
+        <v>-38.475724</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18533,10 +18641,10 @@
         <v>868</v>
       </c>
       <c r="V178" s="5" t="n">
-        <v>-3.7243067</v>
+        <v>-3.724134</v>
       </c>
       <c r="W178" s="5" t="n">
-        <v>-38.5530314</v>
+        <v>-38.554139</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18592,10 +18700,10 @@
         <v>872</v>
       </c>
       <c r="V179" s="5" t="n">
-        <v>-3.723874</v>
+        <v>-3.723879</v>
       </c>
       <c r="W179" s="5" t="n">
-        <v>-38.4770822</v>
+        <v>-38.477082</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18651,10 +18759,10 @@
         <v>876</v>
       </c>
       <c r="V180" s="5" t="n">
-        <v>-3.7841268</v>
+        <v>-3.784141</v>
       </c>
       <c r="W180" s="5" t="n">
-        <v>-38.5877994</v>
+        <v>-38.587824</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18710,10 +18818,10 @@
         <v>880</v>
       </c>
       <c r="V181" s="5" t="n">
-        <v>-3.7680406</v>
+        <v>-3.767666</v>
       </c>
       <c r="W181" s="5" t="n">
-        <v>-38.4940825</v>
+        <v>-38.493892</v>
       </c>
     </row>
     <row r="182" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18769,10 +18877,10 @@
         <v>884</v>
       </c>
       <c r="V182" s="5" t="n">
-        <v>-3.7193323</v>
+        <v>-3.719332</v>
       </c>
       <c r="W182" s="5" t="n">
-        <v>-38.5178001</v>
+        <v>-38.517791</v>
       </c>
     </row>
     <row r="183" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18828,10 +18936,10 @@
         <v>405</v>
       </c>
       <c r="V183" s="5" t="n">
-        <v>-3.7647783</v>
+        <v>-3.764928</v>
       </c>
       <c r="W183" s="5" t="n">
-        <v>-38.5791536</v>
+        <v>-38.578898</v>
       </c>
     </row>
     <row r="184" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18887,10 +18995,10 @@
         <v>890</v>
       </c>
       <c r="V184" s="5" t="n">
-        <v>-3.706945</v>
+        <v>-3.706115</v>
       </c>
       <c r="W184" s="5" t="n">
-        <v>-38.5629433</v>
+        <v>-38.563456</v>
       </c>
     </row>
     <row r="185" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -18946,10 +19054,10 @@
         <v>894</v>
       </c>
       <c r="V185" s="5" t="n">
-        <v>-3.7530125</v>
+        <v>-3.753587</v>
       </c>
       <c r="W185" s="5" t="n">
-        <v>-38.581155</v>
+        <v>-38.581783</v>
       </c>
     </row>
     <row r="186" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19005,10 +19113,10 @@
         <v>898</v>
       </c>
       <c r="V186" s="5" t="n">
-        <v>-3.8462812</v>
+        <v>-3.846281</v>
       </c>
       <c r="W186" s="5" t="n">
-        <v>-38.5231242</v>
+        <v>-38.523124</v>
       </c>
     </row>
     <row r="187" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19064,10 +19172,10 @@
         <v>902</v>
       </c>
       <c r="V187" s="5" t="n">
-        <v>-3.8889429</v>
+        <v>-3.888949</v>
       </c>
       <c r="W187" s="5" t="n">
-        <v>-38.5089786</v>
+        <v>-38.508964</v>
       </c>
     </row>
     <row r="188" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19123,7 +19231,7 @@
         <v>906</v>
       </c>
       <c r="V188" s="5" t="n">
-        <v>-3.7228557</v>
+        <v>-3.722856</v>
       </c>
       <c r="W188" s="5" t="n">
         <v>-38.583501</v>
@@ -19182,10 +19290,10 @@
         <v>910</v>
       </c>
       <c r="V189" s="5" t="n">
-        <v>-3.7867444</v>
+        <v>-3.782942</v>
       </c>
       <c r="W189" s="5" t="n">
-        <v>-38.6207004</v>
+        <v>-38.619358</v>
       </c>
     </row>
     <row r="190" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19243,10 +19351,10 @@
         <v>914</v>
       </c>
       <c r="V190" s="5" t="n">
-        <v>-3.7132596</v>
+        <v>-3.71364</v>
       </c>
       <c r="W190" s="5" t="n">
-        <v>-38.4664397</v>
+        <v>-38.466607</v>
       </c>
     </row>
     <row r="191" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19302,10 +19410,10 @@
         <v>489</v>
       </c>
       <c r="V191" s="5" t="n">
-        <v>-3.827559</v>
+        <v>-3.829823</v>
       </c>
       <c r="W191" s="5" t="n">
-        <v>-38.5900057</v>
+        <v>-38.590793</v>
       </c>
     </row>
     <row r="192" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19369,10 +19477,10 @@
         <v>921</v>
       </c>
       <c r="V192" s="5" t="n">
-        <v>-3.8225775</v>
+        <v>-3.821899</v>
       </c>
       <c r="W192" s="5" t="n">
-        <v>-38.6075296</v>
+        <v>-38.608277</v>
       </c>
     </row>
     <row r="193" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19429,8 +19537,12 @@
       <c r="U193" s="5" t="s">
         <v>925</v>
       </c>
-      <c r="V193" s="5"/>
-      <c r="W193" s="5"/>
+      <c r="V193" s="5" t="n">
+        <v>-3.769582</v>
+      </c>
+      <c r="W193" s="5" t="n">
+        <v>-38.495851</v>
+      </c>
     </row>
     <row r="194" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="5" t="s">
@@ -19487,10 +19599,10 @@
         <v>929</v>
       </c>
       <c r="V194" s="5" t="n">
-        <v>-3.7651707</v>
+        <v>-3.765263</v>
       </c>
       <c r="W194" s="5" t="n">
-        <v>-38.4407156</v>
+        <v>-38.440862</v>
       </c>
     </row>
     <row r="195" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19546,10 +19658,10 @@
         <v>933</v>
       </c>
       <c r="V195" s="5" t="n">
-        <v>-3.8395447</v>
+        <v>-3.837795</v>
       </c>
       <c r="W195" s="5" t="n">
-        <v>-38.5591561</v>
+        <v>-38.558308</v>
       </c>
     </row>
     <row r="196" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19607,10 +19719,10 @@
         <v>813</v>
       </c>
       <c r="V196" s="5" t="n">
-        <v>-3.7219669</v>
+        <v>-3.722395</v>
       </c>
       <c r="W196" s="5" t="n">
-        <v>-38.4674257</v>
+        <v>-38.471827</v>
       </c>
     </row>
     <row r="197" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19666,7 +19778,7 @@
         <v>939</v>
       </c>
       <c r="V197" s="5" t="n">
-        <v>-3.7362802</v>
+        <v>-3.73628</v>
       </c>
       <c r="W197" s="5" t="n">
         <v>-38.590628</v>
@@ -19725,10 +19837,10 @@
         <v>943</v>
       </c>
       <c r="V198" s="5" t="n">
-        <v>-3.8409881</v>
+        <v>-3.842373</v>
       </c>
       <c r="W198" s="5" t="n">
-        <v>-38.5163431</v>
+        <v>-38.514793</v>
       </c>
     </row>
     <row r="199" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19786,10 +19898,10 @@
         <v>947</v>
       </c>
       <c r="V199" s="5" t="n">
-        <v>-3.7481877</v>
+        <v>-3.750064</v>
       </c>
       <c r="W199" s="5" t="n">
-        <v>-38.5643329</v>
+        <v>-38.562222</v>
       </c>
     </row>
     <row r="200" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19845,10 +19957,10 @@
         <v>951</v>
       </c>
       <c r="V200" s="5" t="n">
-        <v>-3.7091321</v>
+        <v>-3.709179</v>
       </c>
       <c r="W200" s="5" t="n">
-        <v>-38.5586555</v>
+        <v>-38.558593</v>
       </c>
     </row>
     <row r="201" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -19911,8 +20023,12 @@
       <c r="U201" s="5" t="s">
         <v>956</v>
       </c>
-      <c r="V201" s="5"/>
-      <c r="W201" s="5"/>
+      <c r="V201" s="5" t="n">
+        <v>-3.817534</v>
+      </c>
+      <c r="W201" s="5" t="n">
+        <v>-38.60244</v>
+      </c>
     </row>
     <row r="202" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="5" t="s">
@@ -19967,10 +20083,10 @@
         <v>960</v>
       </c>
       <c r="V202" s="5" t="n">
-        <v>-3.7262124</v>
+        <v>-3.726224</v>
       </c>
       <c r="W202" s="5" t="n">
-        <v>-38.5984927</v>
+        <v>-38.598494</v>
       </c>
     </row>
     <row r="203" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20028,10 +20144,10 @@
         <v>964</v>
       </c>
       <c r="V203" s="5" t="n">
-        <v>-3.7626343</v>
+        <v>-3.762576</v>
       </c>
       <c r="W203" s="5" t="n">
-        <v>-38.6108636</v>
+        <v>-38.611886</v>
       </c>
     </row>
     <row r="204" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20087,10 +20203,10 @@
         <v>968</v>
       </c>
       <c r="V204" s="5" t="n">
-        <v>-3.7498652</v>
+        <v>-3.749865</v>
       </c>
       <c r="W204" s="5" t="n">
-        <v>-38.5909952</v>
+        <v>-38.590995</v>
       </c>
     </row>
     <row r="205" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20154,10 +20270,10 @@
         <v>973</v>
       </c>
       <c r="V205" s="5" t="n">
-        <v>-3.7940624</v>
+        <v>-3.79461</v>
       </c>
       <c r="W205" s="5" t="n">
-        <v>-38.5163581</v>
+        <v>-38.515378</v>
       </c>
     </row>
     <row r="206" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20215,10 +20331,10 @@
         <v>977</v>
       </c>
       <c r="V206" s="5" t="n">
-        <v>-3.8524034</v>
+        <v>-3.851489</v>
       </c>
       <c r="W206" s="5" t="n">
-        <v>-38.4994765</v>
+        <v>-38.502834</v>
       </c>
     </row>
     <row r="207" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20276,10 +20392,10 @@
         <v>981</v>
       </c>
       <c r="V207" s="5" t="n">
-        <v>-3.7177687</v>
+        <v>-3.720209</v>
       </c>
       <c r="W207" s="5" t="n">
-        <v>-38.576288</v>
+        <v>-38.572865</v>
       </c>
     </row>
     <row r="208" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20337,10 +20453,10 @@
         <v>985</v>
       </c>
       <c r="V208" s="5" t="n">
-        <v>-3.7836831</v>
+        <v>-3.784729</v>
       </c>
       <c r="W208" s="5" t="n">
-        <v>-38.5384435</v>
+        <v>-38.53909</v>
       </c>
     </row>
     <row r="209" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20397,8 +20513,12 @@
       <c r="U209" s="5" t="s">
         <v>990</v>
       </c>
-      <c r="V209" s="5"/>
-      <c r="W209" s="5"/>
+      <c r="V209" s="5" t="n">
+        <v>-3.836506</v>
+      </c>
+      <c r="W209" s="5" t="n">
+        <v>-38.478645</v>
+      </c>
     </row>
     <row r="210" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="5" t="s">
@@ -20455,10 +20575,10 @@
         <v>994</v>
       </c>
       <c r="V210" s="5" t="n">
-        <v>-3.8348126</v>
+        <v>-3.834826</v>
       </c>
       <c r="W210" s="5" t="n">
-        <v>-38.5658869</v>
+        <v>-38.564799</v>
       </c>
     </row>
     <row r="211" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20516,10 +20636,10 @@
         <v>998</v>
       </c>
       <c r="V211" s="5" t="n">
-        <v>-3.7742466</v>
+        <v>-3.773749</v>
       </c>
       <c r="W211" s="5" t="n">
-        <v>-38.4684469</v>
+        <v>-38.468876</v>
       </c>
     </row>
     <row r="212" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20576,8 +20696,12 @@
       <c r="U212" s="5" t="s">
         <v>1002</v>
       </c>
-      <c r="V212" s="5"/>
-      <c r="W212" s="5"/>
+      <c r="V212" s="5" t="n">
+        <v>-3.83229</v>
+      </c>
+      <c r="W212" s="5" t="n">
+        <v>-38.535727</v>
+      </c>
     </row>
     <row r="213" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="5" t="s">
@@ -20634,10 +20758,10 @@
         <v>1007</v>
       </c>
       <c r="V213" s="5" t="n">
-        <v>-3.8037579</v>
+        <v>-3.804442</v>
       </c>
       <c r="W213" s="5" t="n">
-        <v>-38.4612645</v>
+        <v>-38.461214</v>
       </c>
     </row>
     <row r="214" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20695,10 +20819,10 @@
         <v>1011</v>
       </c>
       <c r="V214" s="5" t="n">
-        <v>-3.8522103</v>
+        <v>-3.852591</v>
       </c>
       <c r="W214" s="5" t="n">
-        <v>-38.479968</v>
+        <v>-38.480227</v>
       </c>
     </row>
     <row r="215" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20755,8 +20879,12 @@
       <c r="U215" s="5" t="s">
         <v>1015</v>
       </c>
-      <c r="V215" s="5"/>
-      <c r="W215" s="5"/>
+      <c r="V215" s="5" t="n">
+        <v>-3.802243</v>
+      </c>
+      <c r="W215" s="5" t="n">
+        <v>-38.552965</v>
+      </c>
     </row>
     <row r="216" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="5" t="s">
@@ -20813,10 +20941,10 @@
         <v>1019</v>
       </c>
       <c r="V216" s="5" t="n">
-        <v>-3.8248288</v>
+        <v>-3.822939</v>
       </c>
       <c r="W216" s="5" t="n">
-        <v>-38.5542762</v>
+        <v>-38.554175</v>
       </c>
     </row>
     <row r="217" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -20873,8 +21001,12 @@
       <c r="U217" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="V217" s="5"/>
-      <c r="W217" s="5"/>
+      <c r="V217" s="5" t="n">
+        <v>-3.722935</v>
+      </c>
+      <c r="W217" s="5" t="n">
+        <v>-38.472766</v>
+      </c>
     </row>
     <row r="218" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="5" t="s">
@@ -20936,8 +21068,12 @@
       <c r="U218" s="5" t="s">
         <v>1028</v>
       </c>
-      <c r="V218" s="5"/>
-      <c r="W218" s="5"/>
+      <c r="V218" s="5" t="n">
+        <v>-3.694996</v>
+      </c>
+      <c r="W218" s="5" t="n">
+        <v>-38.581937</v>
+      </c>
     </row>
     <row r="219" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="5" t="s">
@@ -21000,10 +21136,10 @@
         <v>1034</v>
       </c>
       <c r="V219" s="5" t="n">
-        <v>-3.7232135</v>
+        <v>-3.723191</v>
       </c>
       <c r="W219" s="5" t="n">
-        <v>-38.5614656</v>
+        <v>-38.56147</v>
       </c>
     </row>
     <row r="220" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21067,10 +21203,10 @@
         <v>1039</v>
       </c>
       <c r="V220" s="5" t="n">
-        <v>-3.7445337</v>
+        <v>-3.744579</v>
       </c>
       <c r="W220" s="5" t="n">
-        <v>-38.4549604</v>
+        <v>-38.45498</v>
       </c>
     </row>
     <row r="221" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21134,10 +21270,10 @@
         <v>1044</v>
       </c>
       <c r="V221" s="5" t="n">
-        <v>-3.8456721</v>
+        <v>-3.844235</v>
       </c>
       <c r="W221" s="5" t="n">
-        <v>-38.5068633</v>
+        <v>-38.50649</v>
       </c>
     </row>
     <row r="222" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21201,10 +21337,10 @@
         <v>1049</v>
       </c>
       <c r="V222" s="5" t="n">
-        <v>-3.7563972</v>
+        <v>-3.756552</v>
       </c>
       <c r="W222" s="5" t="n">
-        <v>-38.4684519</v>
+        <v>-38.468486</v>
       </c>
     </row>
     <row r="223" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21268,10 +21404,10 @@
         <v>1054</v>
       </c>
       <c r="V223" s="5" t="n">
-        <v>-3.8089033</v>
+        <v>-3.809792</v>
       </c>
       <c r="W223" s="5" t="n">
-        <v>-38.5162216</v>
+        <v>-38.516221</v>
       </c>
     </row>
     <row r="224" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21329,10 +21465,10 @@
         <v>1058</v>
       </c>
       <c r="V224" s="5" t="n">
-        <v>-3.7920774</v>
+        <v>-3.792145</v>
       </c>
       <c r="W224" s="5" t="n">
-        <v>-38.5616308</v>
+        <v>-38.560943</v>
       </c>
     </row>
     <row r="225" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21394,10 +21530,10 @@
         <v>1063</v>
       </c>
       <c r="V225" s="5" t="n">
-        <v>-3.8321159</v>
+        <v>-3.83203</v>
       </c>
       <c r="W225" s="5" t="n">
-        <v>-38.5660569</v>
+        <v>-38.56614</v>
       </c>
     </row>
     <row r="226" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21453,10 +21589,10 @@
         <v>1067</v>
       </c>
       <c r="V226" s="5" t="n">
-        <v>-3.7248665</v>
+        <v>-3.724731</v>
       </c>
       <c r="W226" s="5" t="n">
-        <v>-38.591557</v>
+        <v>-38.591454</v>
       </c>
     </row>
     <row r="227" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21512,10 +21648,10 @@
         <v>1071</v>
       </c>
       <c r="V227" s="5" t="n">
-        <v>-3.7836054</v>
+        <v>-3.783498</v>
       </c>
       <c r="W227" s="5" t="n">
-        <v>-38.5959424</v>
+        <v>-38.595967</v>
       </c>
     </row>
     <row r="228" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21571,10 +21707,10 @@
         <v>200</v>
       </c>
       <c r="V228" s="5" t="n">
-        <v>-3.7198691</v>
+        <v>-3.719869</v>
       </c>
       <c r="W228" s="5" t="n">
-        <v>-38.6060014</v>
+        <v>-38.606001</v>
       </c>
     </row>
     <row r="229" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21632,10 +21768,10 @@
         <v>1078</v>
       </c>
       <c r="V229" s="5" t="n">
-        <v>-3.7720393</v>
+        <v>-3.7726</v>
       </c>
       <c r="W229" s="5" t="n">
-        <v>-38.5398362</v>
+        <v>-38.5283</v>
       </c>
     </row>
     <row r="230" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21699,10 +21835,10 @@
         <v>1083</v>
       </c>
       <c r="V230" s="5" t="n">
-        <v>-3.724464</v>
+        <v>-3.72461</v>
       </c>
       <c r="W230" s="5" t="n">
-        <v>-38.5690052</v>
+        <v>-38.568613</v>
       </c>
     </row>
     <row r="231" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21758,10 +21894,10 @@
         <v>1088</v>
       </c>
       <c r="V231" s="5" t="n">
-        <v>-3.7453495</v>
+        <v>-3.745374</v>
       </c>
       <c r="W231" s="5" t="n">
-        <v>-38.56009</v>
+        <v>-38.560082</v>
       </c>
     </row>
     <row r="232" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21825,10 +21961,10 @@
         <v>1093</v>
       </c>
       <c r="V232" s="5" t="n">
-        <v>-3.7375332</v>
+        <v>-3.737295</v>
       </c>
       <c r="W232" s="5" t="n">
-        <v>-38.5983711</v>
+        <v>-38.598497</v>
       </c>
     </row>
     <row r="233" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21886,10 +22022,10 @@
         <v>1097</v>
       </c>
       <c r="V233" s="5" t="n">
-        <v>-3.7737585</v>
+        <v>-3.77243</v>
       </c>
       <c r="W233" s="5" t="n">
-        <v>-38.4876784</v>
+        <v>-38.49129</v>
       </c>
     </row>
     <row r="234" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -21944,8 +22080,12 @@
       <c r="U234" s="5" t="s">
         <v>1101</v>
       </c>
-      <c r="V234" s="5"/>
-      <c r="W234" s="5"/>
+      <c r="V234" s="5" t="n">
+        <v>-3.723302</v>
+      </c>
+      <c r="W234" s="5" t="n">
+        <v>-38.588693</v>
+      </c>
     </row>
     <row r="235" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="5" t="s">
@@ -22001,8 +22141,12 @@
       <c r="U235" s="5" t="s">
         <v>1105</v>
       </c>
-      <c r="V235" s="5"/>
-      <c r="W235" s="5"/>
+      <c r="V235" s="5" t="n">
+        <v>-3.856514</v>
+      </c>
+      <c r="W235" s="5" t="n">
+        <v>-38.510244</v>
+      </c>
     </row>
     <row r="236" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="5" t="s">
@@ -22057,10 +22201,10 @@
         <v>1109</v>
       </c>
       <c r="V236" s="5" t="n">
-        <v>-3.8072638</v>
+        <v>-3.80726</v>
       </c>
       <c r="W236" s="5" t="n">
-        <v>-38.5973907</v>
+        <v>-38.59743</v>
       </c>
     </row>
     <row r="237" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22118,10 +22262,10 @@
         <v>1113</v>
       </c>
       <c r="V237" s="5" t="n">
-        <v>-3.7874942</v>
+        <v>-3.786002</v>
       </c>
       <c r="W237" s="5" t="n">
-        <v>-38.6014649</v>
+        <v>-38.604877</v>
       </c>
     </row>
     <row r="238" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22177,10 +22321,10 @@
         <v>1118</v>
       </c>
       <c r="V238" s="5" t="n">
-        <v>-3.7951258</v>
+        <v>-3.795126</v>
       </c>
       <c r="W238" s="5" t="n">
-        <v>-38.5637109</v>
+        <v>-38.563711</v>
       </c>
     </row>
     <row r="239" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22236,10 +22380,10 @@
         <v>1122</v>
       </c>
       <c r="V239" s="5" t="n">
-        <v>-3.8126166</v>
+        <v>-3.812617</v>
       </c>
       <c r="W239" s="5" t="n">
-        <v>-38.5181403</v>
+        <v>-38.51814</v>
       </c>
     </row>
     <row r="240" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22295,10 +22439,10 @@
         <v>1126</v>
       </c>
       <c r="V240" s="5" t="n">
-        <v>-3.8461374</v>
+        <v>-3.84603</v>
       </c>
       <c r="W240" s="5" t="n">
-        <v>-38.5235864</v>
+        <v>-38.523572</v>
       </c>
     </row>
     <row r="241" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22354,10 +22498,10 @@
         <v>1130</v>
       </c>
       <c r="V241" s="5" t="n">
-        <v>-3.8293846</v>
+        <v>-3.829418</v>
       </c>
       <c r="W241" s="5" t="n">
-        <v>-38.5557003</v>
+        <v>-38.555419</v>
       </c>
     </row>
     <row r="242" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22421,10 +22565,10 @@
         <v>1135</v>
       </c>
       <c r="V242" s="5" t="n">
-        <v>-3.8045609</v>
+        <v>-3.804506</v>
       </c>
       <c r="W242" s="5" t="n">
-        <v>-38.6115707</v>
+        <v>-38.611813</v>
       </c>
     </row>
     <row r="243" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22482,10 +22626,10 @@
         <v>1139</v>
       </c>
       <c r="V243" s="5" t="n">
-        <v>-3.7132596</v>
+        <v>-3.714313</v>
       </c>
       <c r="W243" s="5" t="n">
-        <v>-38.4664397</v>
+        <v>-38.466327</v>
       </c>
     </row>
     <row r="244" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22542,8 +22686,12 @@
       <c r="U244" s="5" t="s">
         <v>1143</v>
       </c>
-      <c r="V244" s="5"/>
-      <c r="W244" s="5"/>
+      <c r="V244" s="5" t="n">
+        <v>-3.799259</v>
+      </c>
+      <c r="W244" s="5" t="n">
+        <v>-38.548491</v>
+      </c>
     </row>
     <row r="245" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="5" t="s">
@@ -22600,10 +22748,10 @@
         <v>1147</v>
       </c>
       <c r="V245" s="5" t="n">
-        <v>-3.7609021</v>
+        <v>-3.759826</v>
       </c>
       <c r="W245" s="5" t="n">
-        <v>-38.5821656</v>
+        <v>-38.583461</v>
       </c>
     </row>
     <row r="246" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22660,8 +22808,12 @@
       <c r="U246" s="5" t="s">
         <v>1151</v>
       </c>
-      <c r="V246" s="5"/>
-      <c r="W246" s="5"/>
+      <c r="V246" s="5" t="n">
+        <v>-3.828652</v>
+      </c>
+      <c r="W246" s="5" t="n">
+        <v>-38.544982</v>
+      </c>
     </row>
     <row r="247" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="5" t="s">
@@ -22717,8 +22869,12 @@
       <c r="U247" s="5" t="s">
         <v>1155</v>
       </c>
-      <c r="V247" s="5"/>
-      <c r="W247" s="5"/>
+      <c r="V247" s="5" t="n">
+        <v>-3.847468</v>
+      </c>
+      <c r="W247" s="5" t="n">
+        <v>-38.55418</v>
+      </c>
     </row>
     <row r="248" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="5" t="s">
@@ -22775,10 +22931,10 @@
         <v>1159</v>
       </c>
       <c r="V248" s="5" t="n">
-        <v>-3.858067</v>
+        <v>-3.858769</v>
       </c>
       <c r="W248" s="5" t="n">
-        <v>-38.5152759</v>
+        <v>-38.515268</v>
       </c>
     </row>
     <row r="249" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22836,10 +22992,10 @@
         <v>1164</v>
       </c>
       <c r="V249" s="5" t="n">
-        <v>-3.752606</v>
+        <v>-3.752845</v>
       </c>
       <c r="W249" s="5" t="n">
-        <v>-38.4732107</v>
+        <v>-38.47289</v>
       </c>
     </row>
     <row r="250" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22897,10 +23053,10 @@
         <v>1168</v>
       </c>
       <c r="V250" s="5" t="n">
-        <v>-3.7408411</v>
+        <v>-3.745273</v>
       </c>
       <c r="W250" s="5" t="n">
-        <v>-38.549837</v>
+        <v>-38.554139</v>
       </c>
     </row>
     <row r="251" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -22956,10 +23112,10 @@
         <v>1172</v>
       </c>
       <c r="V251" s="5" t="n">
-        <v>-3.7494594</v>
+        <v>-3.749468</v>
       </c>
       <c r="W251" s="5" t="n">
-        <v>-38.5623371</v>
+        <v>-38.562366</v>
       </c>
     </row>
     <row r="252" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23017,10 +23173,10 @@
         <v>1176</v>
       </c>
       <c r="V252" s="5" t="n">
-        <v>-3.7662222</v>
+        <v>-3.766722</v>
       </c>
       <c r="W252" s="5" t="n">
-        <v>-38.603876</v>
+        <v>-38.604123</v>
       </c>
     </row>
     <row r="253" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23078,10 +23234,10 @@
         <v>1180</v>
       </c>
       <c r="V253" s="5" t="n">
-        <v>-3.7510869</v>
+        <v>-3.754029</v>
       </c>
       <c r="W253" s="5" t="n">
-        <v>-38.5944563</v>
+        <v>-38.595328</v>
       </c>
     </row>
     <row r="254" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23138,8 +23294,12 @@
       <c r="U254" s="5" t="s">
         <v>1184</v>
       </c>
-      <c r="V254" s="5"/>
-      <c r="W254" s="5"/>
+      <c r="V254" s="5" t="n">
+        <v>-3.738321</v>
+      </c>
+      <c r="W254" s="5" t="n">
+        <v>-38.595177</v>
+      </c>
     </row>
     <row r="255" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A255" s="5" t="s">
@@ -23202,10 +23362,10 @@
         <v>1189</v>
       </c>
       <c r="V255" s="5" t="n">
-        <v>-3.7491792</v>
+        <v>-3.749268</v>
       </c>
       <c r="W255" s="5" t="n">
-        <v>-38.5618209</v>
+        <v>-38.561723</v>
       </c>
     </row>
     <row r="256" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23261,10 +23421,10 @@
         <v>1193</v>
       </c>
       <c r="V256" s="5" t="n">
-        <v>-3.7671146</v>
+        <v>-3.766692</v>
       </c>
       <c r="W256" s="5" t="n">
-        <v>-38.60477</v>
+        <v>-38.605845</v>
       </c>
     </row>
     <row r="257" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23320,10 +23480,10 @@
         <v>1197</v>
       </c>
       <c r="V257" s="5" t="n">
-        <v>-3.7810147</v>
+        <v>-3.780895</v>
       </c>
       <c r="W257" s="5" t="n">
-        <v>-38.572098</v>
+        <v>-38.57268</v>
       </c>
     </row>
     <row r="258" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23379,10 +23539,10 @@
         <v>1201</v>
       </c>
       <c r="V258" s="5" t="n">
-        <v>-3.7539276</v>
+        <v>-3.75501</v>
       </c>
       <c r="W258" s="5" t="n">
-        <v>-38.5949627</v>
+        <v>-38.595401</v>
       </c>
     </row>
     <row r="259" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23439,8 +23599,12 @@
       <c r="U259" s="5" t="s">
         <v>1205</v>
       </c>
-      <c r="V259" s="5"/>
-      <c r="W259" s="5"/>
+      <c r="V259" s="5" t="n">
+        <v>-3.815157</v>
+      </c>
+      <c r="W259" s="5" t="n">
+        <v>-38.616052</v>
+      </c>
     </row>
     <row r="260" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A260" s="5" t="s">
@@ -23496,8 +23660,12 @@
       <c r="U260" s="5" t="s">
         <v>1209</v>
       </c>
-      <c r="V260" s="5"/>
-      <c r="W260" s="5"/>
+      <c r="V260" s="5" t="n">
+        <v>-3.797175</v>
+      </c>
+      <c r="W260" s="5" t="n">
+        <v>-38.613528</v>
+      </c>
     </row>
     <row r="261" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A261" s="5" t="s">
@@ -23560,10 +23728,10 @@
         <v>1215</v>
       </c>
       <c r="V261" s="5" t="n">
-        <v>-3.7911038</v>
+        <v>-3.786305</v>
       </c>
       <c r="W261" s="5" t="n">
-        <v>-38.5836432</v>
+        <v>-38.579504</v>
       </c>
     </row>
     <row r="262" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23621,10 +23789,10 @@
         <v>1219</v>
       </c>
       <c r="V262" s="5" t="n">
-        <v>-3.7135333</v>
+        <v>-3.713549</v>
       </c>
       <c r="W262" s="5" t="n">
-        <v>-38.6005827</v>
+        <v>-38.60055</v>
       </c>
     </row>
     <row r="263" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23688,10 +23856,10 @@
         <v>1224</v>
       </c>
       <c r="V263" s="5" t="n">
-        <v>-3.7185061</v>
+        <v>-3.7185</v>
       </c>
       <c r="W263" s="5" t="n">
-        <v>-38.5350759</v>
+        <v>-38.535146</v>
       </c>
     </row>
     <row r="264" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23757,7 +23925,7 @@
         <v>1231</v>
       </c>
       <c r="V264" s="5" t="n">
-        <v>-3.8176793</v>
+        <v>-3.817679</v>
       </c>
       <c r="W264" s="5" t="n">
         <v>-38.617243</v>
@@ -23822,10 +23990,10 @@
         <v>1236</v>
       </c>
       <c r="V265" s="5" t="n">
-        <v>-3.7184607</v>
+        <v>-3.718469</v>
       </c>
       <c r="W265" s="5" t="n">
-        <v>-38.6030173</v>
+        <v>-38.60302</v>
       </c>
     </row>
     <row r="266" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23887,10 +24055,10 @@
         <v>1241</v>
       </c>
       <c r="V266" s="5" t="n">
-        <v>-3.7307479</v>
+        <v>-3.730961</v>
       </c>
       <c r="W266" s="5" t="n">
-        <v>-38.5809714</v>
+        <v>-38.581272</v>
       </c>
     </row>
     <row r="267" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -23946,10 +24114,10 @@
         <v>339</v>
       </c>
       <c r="V267" s="5" t="n">
-        <v>-3.7772557</v>
+        <v>-3.776928</v>
       </c>
       <c r="W267" s="5" t="n">
-        <v>-38.6173674</v>
+        <v>-38.617501</v>
       </c>
     </row>
     <row r="268" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24013,10 +24181,10 @@
         <v>1248</v>
       </c>
       <c r="V268" s="5" t="n">
-        <v>-3.7259601</v>
+        <v>-3.726144</v>
       </c>
       <c r="W268" s="5" t="n">
-        <v>-38.5461982</v>
+        <v>-38.546197</v>
       </c>
     </row>
     <row r="269" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24074,10 +24242,10 @@
         <v>1252</v>
       </c>
       <c r="V269" s="5" t="n">
-        <v>-3.8757462</v>
+        <v>-3.878191</v>
       </c>
       <c r="W269" s="5" t="n">
-        <v>-38.5153349</v>
+        <v>-38.514833</v>
       </c>
     </row>
     <row r="270" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24133,10 +24301,10 @@
         <v>1256</v>
       </c>
       <c r="V270" s="5" t="n">
-        <v>-3.7569323</v>
+        <v>-3.749406</v>
       </c>
       <c r="W270" s="5" t="n">
-        <v>-38.596963</v>
+        <v>-38.595859</v>
       </c>
     </row>
     <row r="271" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24192,10 +24360,10 @@
         <v>1261</v>
       </c>
       <c r="V271" s="5" t="n">
-        <v>-3.7690213</v>
+        <v>-3.768031</v>
       </c>
       <c r="W271" s="5" t="n">
-        <v>-38.5904807</v>
+        <v>-38.590316</v>
       </c>
     </row>
     <row r="272" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24253,10 +24421,10 @@
         <v>1252</v>
       </c>
       <c r="V272" s="5" t="n">
-        <v>-3.8757462</v>
+        <v>-3.878448</v>
       </c>
       <c r="W272" s="5" t="n">
-        <v>-38.5153349</v>
+        <v>-38.514579</v>
       </c>
     </row>
     <row r="273" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24312,10 +24480,10 @@
         <v>247</v>
       </c>
       <c r="V273" s="5" t="n">
-        <v>-3.7379747</v>
+        <v>-3.738055</v>
       </c>
       <c r="W273" s="5" t="n">
-        <v>-38.4565172</v>
+        <v>-38.456514</v>
       </c>
     </row>
     <row r="274" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24371,10 +24539,10 @@
         <v>1269</v>
       </c>
       <c r="V274" s="5" t="n">
-        <v>-3.7635639</v>
+        <v>-3.762697</v>
       </c>
       <c r="W274" s="5" t="n">
-        <v>-38.5967521</v>
+        <v>-38.596342</v>
       </c>
     </row>
     <row r="275" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24430,10 +24598,10 @@
         <v>1273</v>
       </c>
       <c r="V275" s="5" t="n">
-        <v>-3.7710978</v>
+        <v>-3.771991</v>
       </c>
       <c r="W275" s="5" t="n">
-        <v>-38.6085361</v>
+        <v>-38.607917</v>
       </c>
     </row>
     <row r="276" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24489,10 +24657,10 @@
         <v>1277</v>
       </c>
       <c r="V276" s="5" t="n">
-        <v>-3.7348323</v>
+        <v>-3.734835</v>
       </c>
       <c r="W276" s="5" t="n">
-        <v>-38.4833075</v>
+        <v>-38.483312</v>
       </c>
     </row>
     <row r="277" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24548,10 +24716,10 @@
         <v>1281</v>
       </c>
       <c r="V277" s="5" t="n">
-        <v>-3.7784647</v>
+        <v>-3.778465</v>
       </c>
       <c r="W277" s="5" t="n">
-        <v>-38.5490643</v>
+        <v>-38.549064</v>
       </c>
     </row>
     <row r="278" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24615,10 +24783,10 @@
         <v>1287</v>
       </c>
       <c r="V278" s="5" t="n">
-        <v>-3.7320397</v>
+        <v>-3.732047</v>
       </c>
       <c r="W278" s="5" t="n">
-        <v>-38.5412295</v>
+        <v>-38.541227</v>
       </c>
     </row>
     <row r="279" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24684,10 +24852,10 @@
         <v>1294</v>
       </c>
       <c r="V279" s="5" t="n">
-        <v>-3.839036</v>
+        <v>-3.838495</v>
       </c>
       <c r="W279" s="5" t="n">
-        <v>-38.5029126</v>
+        <v>-38.502062</v>
       </c>
     </row>
     <row r="280" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24745,10 +24913,10 @@
         <v>1298</v>
       </c>
       <c r="V280" s="5" t="n">
-        <v>-3.8046428</v>
+        <v>-3.801629</v>
       </c>
       <c r="W280" s="5" t="n">
-        <v>-38.5586499</v>
+        <v>-38.560056</v>
       </c>
     </row>
     <row r="281" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24806,10 +24974,10 @@
         <v>1303</v>
       </c>
       <c r="V281" s="5" t="n">
-        <v>-3.7636743</v>
+        <v>-3.764103</v>
       </c>
       <c r="W281" s="5" t="n">
-        <v>-38.5101178</v>
+        <v>-38.510449</v>
       </c>
     </row>
     <row r="282" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24867,10 +25035,10 @@
         <v>1307</v>
       </c>
       <c r="V282" s="5" t="n">
-        <v>-3.8224611</v>
+        <v>-3.822287</v>
       </c>
       <c r="W282" s="5" t="n">
-        <v>-38.5987439</v>
+        <v>-38.599984</v>
       </c>
     </row>
     <row r="283" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24928,10 +25096,10 @@
         <v>1311</v>
       </c>
       <c r="V283" s="5" t="n">
-        <v>-3.7923764</v>
+        <v>-3.792342</v>
       </c>
       <c r="W283" s="5" t="n">
-        <v>-38.6018757</v>
+        <v>-38.601843</v>
       </c>
     </row>
     <row r="284" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -24988,8 +25156,12 @@
       <c r="U284" s="5" t="s">
         <v>1315</v>
       </c>
-      <c r="V284" s="5"/>
-      <c r="W284" s="5"/>
+      <c r="V284" s="5" t="n">
+        <v>-3.842997</v>
+      </c>
+      <c r="W284" s="5" t="n">
+        <v>-38.554797</v>
+      </c>
     </row>
     <row r="285" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A285" s="5" t="s">
@@ -25045,8 +25217,12 @@
       <c r="U285" s="5" t="s">
         <v>1319</v>
       </c>
-      <c r="V285" s="5"/>
-      <c r="W285" s="5"/>
+      <c r="V285" s="5" t="n">
+        <v>-3.84292</v>
+      </c>
+      <c r="W285" s="5" t="n">
+        <v>-38.552376</v>
+      </c>
     </row>
     <row r="286" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A286" s="5" t="s">
@@ -25111,10 +25287,10 @@
         <v>1324</v>
       </c>
       <c r="V286" s="5" t="n">
-        <v>-3.8019337</v>
+        <v>-3.803296</v>
       </c>
       <c r="W286" s="5" t="n">
-        <v>-38.619313</v>
+        <v>-38.619974</v>
       </c>
     </row>
     <row r="287" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25180,10 +25356,10 @@
         <v>1331</v>
       </c>
       <c r="V287" s="5" t="n">
-        <v>-3.7338096</v>
+        <v>-3.73381</v>
       </c>
       <c r="W287" s="5" t="n">
-        <v>-38.5890597</v>
+        <v>-38.58906</v>
       </c>
     </row>
     <row r="288" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25249,10 +25425,10 @@
         <v>1336</v>
       </c>
       <c r="V288" s="5" t="n">
-        <v>-3.7916407</v>
+        <v>-3.793865</v>
       </c>
       <c r="W288" s="5" t="n">
-        <v>-38.6004831</v>
+        <v>-38.594389</v>
       </c>
     </row>
     <row r="289" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25318,10 +25494,10 @@
         <v>1343</v>
       </c>
       <c r="V289" s="5" t="n">
-        <v>-3.8051803</v>
+        <v>-3.80518</v>
       </c>
       <c r="W289" s="5" t="n">
-        <v>-38.5537338</v>
+        <v>-38.553734</v>
       </c>
     </row>
     <row r="290" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25377,10 +25553,10 @@
         <v>1347</v>
       </c>
       <c r="V290" s="5" t="n">
-        <v>-3.7319723</v>
+        <v>-3.732481</v>
       </c>
       <c r="W290" s="5" t="n">
-        <v>-38.6016274</v>
+        <v>-38.602035</v>
       </c>
     </row>
     <row r="291" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25436,10 +25612,10 @@
         <v>1351</v>
       </c>
       <c r="V291" s="5" t="n">
-        <v>-3.7328917</v>
+        <v>-3.732926</v>
       </c>
       <c r="W291" s="5" t="n">
-        <v>-38.4784368</v>
+        <v>-38.478403</v>
       </c>
     </row>
     <row r="292" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25496,8 +25672,12 @@
       <c r="U292" s="5" t="s">
         <v>1355</v>
       </c>
-      <c r="V292" s="5"/>
-      <c r="W292" s="5"/>
+      <c r="V292" s="5" t="n">
+        <v>-3.856491</v>
+      </c>
+      <c r="W292" s="5" t="n">
+        <v>-38.488855</v>
+      </c>
     </row>
     <row r="293" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A293" s="5" t="s">
@@ -25552,10 +25732,10 @@
         <v>1359</v>
       </c>
       <c r="V293" s="5" t="n">
-        <v>-3.8352956</v>
+        <v>-3.835346</v>
       </c>
       <c r="W293" s="5" t="n">
-        <v>-38.5779316</v>
+        <v>-38.577904</v>
       </c>
     </row>
     <row r="294" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25611,10 +25791,10 @@
         <v>1363</v>
       </c>
       <c r="V294" s="5" t="n">
-        <v>-3.8394437</v>
+        <v>-3.83866</v>
       </c>
       <c r="W294" s="5" t="n">
-        <v>-38.5784453</v>
+        <v>-38.578374</v>
       </c>
     </row>
     <row r="295" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25672,10 +25852,10 @@
         <v>1367</v>
       </c>
       <c r="V295" s="5" t="n">
-        <v>-3.7073535</v>
+        <v>-3.705955</v>
       </c>
       <c r="W295" s="5" t="n">
-        <v>-38.5819817</v>
+        <v>-38.585029</v>
       </c>
     </row>
     <row r="296" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25731,10 +25911,10 @@
         <v>1371</v>
       </c>
       <c r="V296" s="5" t="n">
-        <v>-3.8335989</v>
+        <v>-3.83356</v>
       </c>
       <c r="W296" s="5" t="n">
-        <v>-38.568543</v>
+        <v>-38.568625</v>
       </c>
     </row>
     <row r="297" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25792,10 +25972,10 @@
         <v>1376</v>
       </c>
       <c r="V297" s="5" t="n">
-        <v>-3.822825</v>
+        <v>-3.821742</v>
       </c>
       <c r="W297" s="5" t="n">
-        <v>-38.4877553</v>
+        <v>-38.492184</v>
       </c>
     </row>
     <row r="298" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25861,10 +26041,10 @@
         <v>1383</v>
       </c>
       <c r="V298" s="5" t="n">
-        <v>-3.7838345</v>
+        <v>-3.784018</v>
       </c>
       <c r="W298" s="5" t="n">
-        <v>-38.5496612</v>
+        <v>-38.549729</v>
       </c>
     </row>
     <row r="299" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25930,10 +26110,10 @@
         <v>1390</v>
       </c>
       <c r="V299" s="5" t="n">
-        <v>-3.8114992</v>
+        <v>-3.811633</v>
       </c>
       <c r="W299" s="5" t="n">
-        <v>-38.5945451</v>
+        <v>-38.594673</v>
       </c>
     </row>
     <row r="300" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25999,10 +26179,10 @@
         <v>1398</v>
       </c>
       <c r="V300" s="5" t="n">
-        <v>-3.7592482</v>
+        <v>-3.759399</v>
       </c>
       <c r="W300" s="5" t="n">
-        <v>-38.5210704</v>
+        <v>-38.520926</v>
       </c>
     </row>
     <row r="301" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26059,8 +26239,12 @@
       <c r="U301" s="5" t="s">
         <v>1402</v>
       </c>
-      <c r="V301" s="5"/>
-      <c r="W301" s="5"/>
+      <c r="V301" s="5" t="n">
+        <v>-3.855174</v>
+      </c>
+      <c r="W301" s="5" t="n">
+        <v>-38.519359</v>
+      </c>
     </row>
     <row r="302" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A302" s="5" t="s">
@@ -26117,10 +26301,10 @@
         <v>1406</v>
       </c>
       <c r="V302" s="5" t="n">
-        <v>-3.7747453</v>
+        <v>-3.771432</v>
       </c>
       <c r="W302" s="5" t="n">
-        <v>-38.6077239</v>
+        <v>-38.607203</v>
       </c>
     </row>
     <row r="303" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26178,10 +26362,10 @@
         <v>1410</v>
       </c>
       <c r="V303" s="5" t="n">
-        <v>-3.7307389</v>
+        <v>-3.730674</v>
       </c>
       <c r="W303" s="5" t="n">
-        <v>-38.5705597</v>
+        <v>-38.570579</v>
       </c>
     </row>
     <row r="304" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26239,10 +26423,10 @@
         <v>1414</v>
       </c>
       <c r="V304" s="5" t="n">
-        <v>-3.7587844</v>
+        <v>-3.758773</v>
       </c>
       <c r="W304" s="5" t="n">
-        <v>-38.5061295</v>
+        <v>-38.506105</v>
       </c>
     </row>
     <row r="305" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26298,10 +26482,10 @@
         <v>1418</v>
       </c>
       <c r="V305" s="5" t="n">
-        <v>-3.7849756</v>
+        <v>-3.784789</v>
       </c>
       <c r="W305" s="5" t="n">
-        <v>-38.5607057</v>
+        <v>-38.560734</v>
       </c>
     </row>
     <row r="306" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26357,10 +26541,10 @@
         <v>1422</v>
       </c>
       <c r="V306" s="5" t="n">
-        <v>-3.742231</v>
+        <v>-3.742198</v>
       </c>
       <c r="W306" s="5" t="n">
-        <v>-38.5895425</v>
+        <v>-38.589319</v>
       </c>
     </row>
     <row r="307" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26418,10 +26602,10 @@
         <v>1428</v>
       </c>
       <c r="V307" s="5" t="n">
-        <v>-3.7888602</v>
+        <v>-3.787567</v>
       </c>
       <c r="W307" s="5" t="n">
-        <v>-38.5255821</v>
+        <v>-38.525482</v>
       </c>
     </row>
     <row r="308" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26479,10 +26663,10 @@
         <v>1432</v>
       </c>
       <c r="V308" s="5" t="n">
-        <v>-3.8670802</v>
+        <v>-3.867331</v>
       </c>
       <c r="W308" s="5" t="n">
-        <v>-38.4941018</v>
+        <v>-38.494011</v>
       </c>
     </row>
     <row r="309" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26538,10 +26722,10 @@
         <v>1436</v>
       </c>
       <c r="V309" s="5" t="n">
-        <v>-3.8303086</v>
+        <v>-3.830319</v>
       </c>
       <c r="W309" s="5" t="n">
-        <v>-38.5585938</v>
+        <v>-38.558624</v>
       </c>
     </row>
     <row r="310" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26596,8 +26780,12 @@
       <c r="U310" s="5" t="s">
         <v>1440</v>
       </c>
-      <c r="V310" s="5"/>
-      <c r="W310" s="5"/>
+      <c r="V310" s="5" t="n">
+        <v>-3.821944</v>
+      </c>
+      <c r="W310" s="5" t="n">
+        <v>-38.533119</v>
+      </c>
     </row>
     <row r="311" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A311" s="5" t="s">
@@ -26655,7 +26843,7 @@
         <v>-3.792456</v>
       </c>
       <c r="W311" s="5" t="n">
-        <v>-38.5439695</v>
+        <v>-38.543969</v>
       </c>
     </row>
     <row r="312" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26711,10 +26899,10 @@
         <v>1448</v>
       </c>
       <c r="V312" s="5" t="n">
-        <v>-3.7998545</v>
+        <v>-3.798212</v>
       </c>
       <c r="W312" s="5" t="n">
-        <v>-38.5452419</v>
+        <v>-38.547312</v>
       </c>
     </row>
     <row r="313" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26769,8 +26957,12 @@
       <c r="U313" s="5" t="s">
         <v>1452</v>
       </c>
-      <c r="V313" s="5"/>
-      <c r="W313" s="5"/>
+      <c r="V313" s="5" t="n">
+        <v>-3.790397</v>
+      </c>
+      <c r="W313" s="5" t="n">
+        <v>-38.534817</v>
+      </c>
     </row>
     <row r="314" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A314" s="5" t="s">
@@ -26825,10 +27017,10 @@
         <v>1456</v>
       </c>
       <c r="V314" s="5" t="n">
-        <v>-3.8227134</v>
+        <v>-3.822644</v>
       </c>
       <c r="W314" s="5" t="n">
-        <v>-38.5547219</v>
+        <v>-38.554835</v>
       </c>
     </row>
     <row r="315" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26884,10 +27076,10 @@
         <v>1460</v>
       </c>
       <c r="V315" s="5" t="n">
-        <v>-3.7497491</v>
+        <v>-3.749739</v>
       </c>
       <c r="W315" s="5" t="n">
-        <v>-38.5220665</v>
+        <v>-38.521923</v>
       </c>
     </row>
     <row r="316" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -26942,8 +27134,12 @@
       <c r="U316" s="5" t="s">
         <v>1464</v>
       </c>
-      <c r="V316" s="5"/>
-      <c r="W316" s="5"/>
+      <c r="V316" s="5" t="n">
+        <v>-3.806946</v>
+      </c>
+      <c r="W316" s="5" t="n">
+        <v>-38.548424</v>
+      </c>
     </row>
     <row r="317" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A317" s="5" t="s">
@@ -27000,10 +27196,10 @@
         <v>1469</v>
       </c>
       <c r="V317" s="5" t="n">
-        <v>-3.7700229</v>
+        <v>-3.772927</v>
       </c>
       <c r="W317" s="5" t="n">
-        <v>-38.5572741</v>
+        <v>-38.558522</v>
       </c>
     </row>
     <row r="318" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27061,10 +27257,10 @@
         <v>1473</v>
       </c>
       <c r="V318" s="5" t="n">
-        <v>-3.8403292</v>
+        <v>-3.839573</v>
       </c>
       <c r="W318" s="5" t="n">
-        <v>-38.5712005</v>
+        <v>-38.571368</v>
       </c>
     </row>
     <row r="319" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27121,8 +27317,12 @@
       <c r="U319" s="5" t="s">
         <v>1477</v>
       </c>
-      <c r="V319" s="5"/>
-      <c r="W319" s="5"/>
+      <c r="V319" s="5" t="n">
+        <v>-3.834195</v>
+      </c>
+      <c r="W319" s="5" t="n">
+        <v>-38.568865</v>
+      </c>
     </row>
     <row r="320" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A320" s="5" t="s">
@@ -27178,8 +27378,12 @@
       <c r="U320" s="5" t="s">
         <v>1481</v>
       </c>
-      <c r="V320" s="5"/>
-      <c r="W320" s="5"/>
+      <c r="V320" s="5" t="n">
+        <v>-3.847428</v>
+      </c>
+      <c r="W320" s="5" t="n">
+        <v>-38.553639</v>
+      </c>
     </row>
     <row r="321" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A321" s="5" t="s">
@@ -27235,8 +27439,12 @@
       <c r="U321" s="5" t="s">
         <v>1485</v>
       </c>
-      <c r="V321" s="5"/>
-      <c r="W321" s="5"/>
+      <c r="V321" s="5" t="n">
+        <v>-3.803738</v>
+      </c>
+      <c r="W321" s="5" t="n">
+        <v>-38.551184</v>
+      </c>
     </row>
     <row r="322" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A322" s="5" t="s">
@@ -27292,8 +27500,12 @@
       <c r="U322" s="5" t="s">
         <v>1489</v>
       </c>
-      <c r="V322" s="5"/>
-      <c r="W322" s="5"/>
+      <c r="V322" s="5" t="n">
+        <v>-3.838406</v>
+      </c>
+      <c r="W322" s="5" t="n">
+        <v>-38.551804</v>
+      </c>
     </row>
     <row r="323" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A323" s="5" t="s">
@@ -27348,10 +27560,10 @@
         <v>1493</v>
       </c>
       <c r="V323" s="5" t="n">
-        <v>-3.7592415</v>
+        <v>-3.758959</v>
       </c>
       <c r="W323" s="5" t="n">
-        <v>-38.5231979</v>
+        <v>-38.523163</v>
       </c>
     </row>
     <row r="324" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27409,10 +27621,10 @@
         <v>147</v>
       </c>
       <c r="V324" s="5" t="n">
-        <v>-3.7657365</v>
+        <v>-3.761419</v>
       </c>
       <c r="W324" s="5" t="n">
-        <v>-38.5502281</v>
+        <v>-38.554762</v>
       </c>
     </row>
     <row r="325" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27470,10 +27682,10 @@
         <v>1499</v>
       </c>
       <c r="V325" s="5" t="n">
-        <v>-3.7737167</v>
+        <v>-3.773231</v>
       </c>
       <c r="W325" s="5" t="n">
-        <v>-38.5309893</v>
+        <v>-38.5281</v>
       </c>
     </row>
     <row r="326" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27531,10 +27743,10 @@
         <v>1504</v>
       </c>
       <c r="V326" s="5" t="n">
-        <v>-3.7569728</v>
+        <v>-3.757087</v>
       </c>
       <c r="W326" s="5" t="n">
-        <v>-38.5494101</v>
+        <v>-38.549201</v>
       </c>
     </row>
     <row r="327" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27590,10 +27802,10 @@
         <v>1508</v>
       </c>
       <c r="V327" s="5" t="n">
-        <v>-3.8115556</v>
+        <v>-3.811532</v>
       </c>
       <c r="W327" s="5" t="n">
-        <v>-38.5964406</v>
+        <v>-38.596455</v>
       </c>
     </row>
     <row r="328" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27649,10 +27861,10 @@
         <v>1512</v>
       </c>
       <c r="V328" s="5" t="n">
-        <v>-3.7887897</v>
+        <v>-3.791817</v>
       </c>
       <c r="W328" s="5" t="n">
-        <v>-38.6068629</v>
+        <v>-38.598146</v>
       </c>
     </row>
     <row r="329" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27708,10 +27920,10 @@
         <v>1516</v>
       </c>
       <c r="V329" s="5" t="n">
-        <v>-3.825897</v>
+        <v>-3.825982</v>
       </c>
       <c r="W329" s="5" t="n">
-        <v>-38.5808698</v>
+        <v>-38.580931</v>
       </c>
     </row>
     <row r="330" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27772,8 +27984,12 @@
       <c r="U330" s="5" t="s">
         <v>1521</v>
       </c>
-      <c r="V330" s="5"/>
-      <c r="W330" s="5"/>
+      <c r="V330" s="5" t="n">
+        <v>-3.817207</v>
+      </c>
+      <c r="W330" s="5" t="n">
+        <v>-38.569704</v>
+      </c>
     </row>
     <row r="331" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A331" s="5" t="s">
@@ -27840,10 +28056,10 @@
         <v>1528</v>
       </c>
       <c r="V331" s="5" t="n">
-        <v>-3.7943989</v>
+        <v>-3.788238</v>
       </c>
       <c r="W331" s="5" t="n">
-        <v>-38.5872951</v>
+        <v>-38.589366</v>
       </c>
     </row>
     <row r="332" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27911,10 +28127,10 @@
         <v>1535</v>
       </c>
       <c r="V332" s="5" t="n">
-        <v>-3.7522239</v>
+        <v>-3.752531</v>
       </c>
       <c r="W332" s="5" t="n">
-        <v>-38.5375209</v>
+        <v>-38.537813</v>
       </c>
     </row>
     <row r="333" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -27970,10 +28186,10 @@
         <v>157</v>
       </c>
       <c r="V333" s="5" t="n">
-        <v>-3.7091052</v>
+        <v>-3.709385</v>
       </c>
       <c r="W333" s="5" t="n">
-        <v>-38.5819017</v>
+        <v>-38.582042</v>
       </c>
     </row>
     <row r="334" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28031,10 +28247,10 @@
         <v>1541</v>
       </c>
       <c r="V334" s="5" t="n">
-        <v>-3.8222969</v>
+        <v>-3.820792</v>
       </c>
       <c r="W334" s="5" t="n">
-        <v>-38.6044058</v>
+        <v>-38.603144</v>
       </c>
     </row>
     <row r="335" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28089,8 +28305,12 @@
       <c r="U335" s="5" t="s">
         <v>1545</v>
       </c>
-      <c r="V335" s="5"/>
-      <c r="W335" s="5"/>
+      <c r="V335" s="5" t="n">
+        <v>-3.72473</v>
+      </c>
+      <c r="W335" s="5" t="n">
+        <v>-38.544545</v>
+      </c>
     </row>
     <row r="336" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A336" s="5" t="s">
@@ -28144,8 +28364,12 @@
       <c r="U336" s="5" t="s">
         <v>1549</v>
       </c>
-      <c r="V336" s="5"/>
-      <c r="W336" s="5"/>
+      <c r="V336" s="5" t="n">
+        <v>-3.824034</v>
+      </c>
+      <c r="W336" s="5" t="n">
+        <v>-38.52004</v>
+      </c>
     </row>
     <row r="337" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A337" s="5" t="s">
@@ -28200,10 +28424,10 @@
         <v>1553</v>
       </c>
       <c r="V337" s="5" t="n">
-        <v>-3.7219373</v>
+        <v>-3.721912</v>
       </c>
       <c r="W337" s="5" t="n">
-        <v>-38.5834176</v>
+        <v>-38.583395</v>
       </c>
     </row>
     <row r="338" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28269,10 +28493,10 @@
         <v>1560</v>
       </c>
       <c r="V338" s="5" t="n">
-        <v>-3.7842832</v>
+        <v>-3.784283</v>
       </c>
       <c r="W338" s="5" t="n">
-        <v>-38.5763469</v>
+        <v>-38.576347</v>
       </c>
     </row>
     <row r="339" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28338,10 +28562,10 @@
         <v>1567</v>
       </c>
       <c r="V339" s="5" t="n">
-        <v>-3.7374283</v>
+        <v>-3.737428</v>
       </c>
       <c r="W339" s="5" t="n">
-        <v>-38.4781494</v>
+        <v>-38.478149</v>
       </c>
     </row>
     <row r="340" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28409,10 +28633,10 @@
         <v>1574</v>
       </c>
       <c r="V340" s="5" t="n">
-        <v>-3.7556828</v>
+        <v>-3.755683</v>
       </c>
       <c r="W340" s="5" t="n">
-        <v>-38.5061655</v>
+        <v>-38.506166</v>
       </c>
     </row>
     <row r="341" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28470,10 +28694,10 @@
         <v>1578</v>
       </c>
       <c r="V341" s="5" t="n">
-        <v>-3.806123</v>
+        <v>-3.805475</v>
       </c>
       <c r="W341" s="5" t="n">
-        <v>-38.6105516</v>
+        <v>-38.611871</v>
       </c>
     </row>
     <row r="342" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28530,8 +28754,12 @@
       <c r="U342" s="5" t="s">
         <v>1582</v>
       </c>
-      <c r="V342" s="5"/>
-      <c r="W342" s="5"/>
+      <c r="V342" s="5" t="n">
+        <v>-3.822755</v>
+      </c>
+      <c r="W342" s="5" t="n">
+        <v>-38.565759</v>
+      </c>
     </row>
     <row r="343" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A343" s="5" t="s">
@@ -28586,10 +28814,10 @@
         <v>1586</v>
       </c>
       <c r="V343" s="5" t="n">
-        <v>-3.7247231</v>
+        <v>-3.724647</v>
       </c>
       <c r="W343" s="5" t="n">
-        <v>-38.5919028</v>
+        <v>-38.591857</v>
       </c>
     </row>
     <row r="344" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28645,10 +28873,10 @@
         <v>1590</v>
       </c>
       <c r="V344" s="5" t="n">
-        <v>-3.8409505</v>
+        <v>-3.840867</v>
       </c>
       <c r="W344" s="5" t="n">
-        <v>-38.5593593</v>
+        <v>-38.55935</v>
       </c>
     </row>
     <row r="345" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28704,10 +28932,10 @@
         <v>122</v>
       </c>
       <c r="V345" s="5" t="n">
-        <v>-3.7060494</v>
+        <v>-3.705429</v>
       </c>
       <c r="W345" s="5" t="n">
-        <v>-38.563909</v>
+        <v>-38.564025</v>
       </c>
     </row>
     <row r="346" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28763,10 +28991,10 @@
         <v>1596</v>
       </c>
       <c r="V346" s="5" t="n">
-        <v>-3.7114347</v>
+        <v>-3.711302</v>
       </c>
       <c r="W346" s="5" t="n">
-        <v>-38.5673924</v>
+        <v>-38.567551</v>
       </c>
     </row>
     <row r="347" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28834,10 +29062,10 @@
         <v>1603</v>
       </c>
       <c r="V347" s="5" t="n">
-        <v>-3.8202916</v>
+        <v>-3.820236</v>
       </c>
       <c r="W347" s="5" t="n">
-        <v>-38.5427452</v>
+        <v>-38.542752</v>
       </c>
     </row>
     <row r="348" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28893,10 +29121,10 @@
         <v>1607</v>
       </c>
       <c r="V348" s="5" t="n">
-        <v>-3.7596033</v>
+        <v>-3.759483</v>
       </c>
       <c r="W348" s="5" t="n">
-        <v>-38.6106766</v>
+        <v>-38.610487</v>
       </c>
     </row>
     <row r="349" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -28952,10 +29180,10 @@
         <v>1611</v>
       </c>
       <c r="V349" s="5" t="n">
-        <v>-3.7645212</v>
+        <v>-3.764556</v>
       </c>
       <c r="W349" s="5" t="n">
-        <v>-38.5097861</v>
+        <v>-38.509767</v>
       </c>
     </row>
     <row r="350" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29012,8 +29240,12 @@
       <c r="U350" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="V350" s="5"/>
-      <c r="W350" s="5"/>
+      <c r="V350" s="5" t="n">
+        <v>-3.807624</v>
+      </c>
+      <c r="W350" s="5" t="n">
+        <v>-38.617719</v>
+      </c>
     </row>
     <row r="351" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A351" s="5" t="s">
@@ -29078,10 +29310,10 @@
         <v>1620</v>
       </c>
       <c r="V351" s="5" t="n">
-        <v>-3.7684807</v>
+        <v>-3.768475</v>
       </c>
       <c r="W351" s="5" t="n">
-        <v>-38.5332756</v>
+        <v>-38.533277</v>
       </c>
     </row>
     <row r="352" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29137,10 +29369,10 @@
         <v>1624</v>
       </c>
       <c r="V352" s="5" t="n">
-        <v>-3.7919522</v>
+        <v>-3.791952</v>
       </c>
       <c r="W352" s="5" t="n">
-        <v>-38.4746985</v>
+        <v>-38.474698</v>
       </c>
     </row>
     <row r="353" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29196,10 +29428,10 @@
         <v>1628</v>
       </c>
       <c r="V353" s="5" t="n">
-        <v>-3.7653353</v>
+        <v>-3.7653</v>
       </c>
       <c r="W353" s="5" t="n">
-        <v>-38.6047711</v>
+        <v>-38.604885</v>
       </c>
     </row>
     <row r="354" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29256,8 +29488,12 @@
       <c r="U354" s="5" t="s">
         <v>1632</v>
       </c>
-      <c r="V354" s="5"/>
-      <c r="W354" s="5"/>
+      <c r="V354" s="5" t="n">
+        <v>-3.8143</v>
+      </c>
+      <c r="W354" s="5" t="n">
+        <v>-38.614922</v>
+      </c>
     </row>
     <row r="355" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A355" s="5" t="s">
@@ -29312,10 +29548,10 @@
         <v>1636</v>
       </c>
       <c r="V355" s="5" t="n">
-        <v>-3.7452742</v>
+        <v>-3.745326</v>
       </c>
       <c r="W355" s="5" t="n">
-        <v>-38.5542775</v>
+        <v>-38.554406</v>
       </c>
     </row>
     <row r="356" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29386,7 +29622,7 @@
         <v>-3.774345</v>
       </c>
       <c r="W356" s="5" t="n">
-        <v>-38.5859545</v>
+        <v>-38.585955</v>
       </c>
     </row>
     <row r="357" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29453,8 +29689,12 @@
       <c r="U357" s="5" t="s">
         <v>1650</v>
       </c>
-      <c r="V357" s="5"/>
-      <c r="W357" s="5"/>
+      <c r="V357" s="5" t="n">
+        <v>-3.80676</v>
+      </c>
+      <c r="W357" s="5" t="n">
+        <v>-38.548862</v>
+      </c>
     </row>
     <row r="358" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A358" s="5" t="s">
@@ -29509,10 +29749,10 @@
         <v>1655</v>
       </c>
       <c r="V358" s="5" t="n">
-        <v>-3.8474034</v>
+        <v>-3.847403</v>
       </c>
       <c r="W358" s="5" t="n">
-        <v>-38.4761219</v>
+        <v>-38.476122</v>
       </c>
     </row>
     <row r="359" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29570,10 +29810,10 @@
         <v>1659</v>
       </c>
       <c r="V359" s="5" t="n">
-        <v>-3.8224611</v>
+        <v>-3.826482</v>
       </c>
       <c r="W359" s="5" t="n">
-        <v>-38.5987439</v>
+        <v>-38.593358</v>
       </c>
     </row>
     <row r="360" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29639,10 +29879,10 @@
         <v>1666</v>
       </c>
       <c r="V360" s="5" t="n">
-        <v>-3.793793</v>
+        <v>-3.793817</v>
       </c>
       <c r="W360" s="5" t="n">
-        <v>-38.6155887</v>
+        <v>-38.61551</v>
       </c>
     </row>
     <row r="361" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29700,10 +29940,10 @@
         <v>1670</v>
       </c>
       <c r="V361" s="5" t="n">
-        <v>-3.8268983</v>
+        <v>-3.827788</v>
       </c>
       <c r="W361" s="5" t="n">
-        <v>-38.5683941</v>
+        <v>-38.569538</v>
       </c>
     </row>
     <row r="362" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29771,10 +30011,10 @@
         <v>1677</v>
       </c>
       <c r="V362" s="5" t="n">
-        <v>-3.8491106</v>
+        <v>-3.845497</v>
       </c>
       <c r="W362" s="5" t="n">
-        <v>-38.4949882</v>
+        <v>-38.495</v>
       </c>
     </row>
     <row r="363" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29830,10 +30070,10 @@
         <v>1681</v>
       </c>
       <c r="V363" s="5" t="n">
-        <v>-3.718234</v>
+        <v>-3.718149</v>
       </c>
       <c r="W363" s="5" t="n">
-        <v>-38.4640378</v>
+        <v>-38.463992</v>
       </c>
     </row>
     <row r="364" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -29900,8 +30140,12 @@
       <c r="U364" s="5" t="s">
         <v>1688</v>
       </c>
-      <c r="V364" s="5"/>
-      <c r="W364" s="5"/>
+      <c r="V364" s="5" t="n">
+        <v>-3.715936</v>
+      </c>
+      <c r="W364" s="5" t="n">
+        <v>-38.598084</v>
+      </c>
     </row>
     <row r="365" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A365" s="5" t="s">
@@ -29956,10 +30200,10 @@
         <v>1553</v>
       </c>
       <c r="V365" s="5" t="n">
-        <v>-3.7219373</v>
+        <v>-3.722244</v>
       </c>
       <c r="W365" s="5" t="n">
-        <v>-38.5834176</v>
+        <v>-38.583443</v>
       </c>
     </row>
     <row r="366" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30015,10 +30259,10 @@
         <v>1694</v>
       </c>
       <c r="V366" s="5" t="n">
-        <v>-3.8385205</v>
+        <v>-3.838489</v>
       </c>
       <c r="W366" s="5" t="n">
-        <v>-38.5137113</v>
+        <v>-38.513679</v>
       </c>
     </row>
     <row r="367" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30074,10 +30318,10 @@
         <v>1698</v>
       </c>
       <c r="V367" s="5" t="n">
-        <v>-3.7231797</v>
+        <v>-3.72311</v>
       </c>
       <c r="W367" s="5" t="n">
-        <v>-38.5702206</v>
+        <v>-38.570183</v>
       </c>
     </row>
     <row r="368" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30135,10 +30379,10 @@
         <v>1702</v>
       </c>
       <c r="V368" s="5" t="n">
-        <v>-3.792127</v>
+        <v>-3.78981</v>
       </c>
       <c r="W368" s="5" t="n">
-        <v>-38.6129797</v>
+        <v>-38.619079</v>
       </c>
     </row>
     <row r="369" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30206,10 +30450,10 @@
         <v>1709</v>
       </c>
       <c r="V369" s="5" t="n">
-        <v>-3.7558085</v>
+        <v>-3.755658</v>
       </c>
       <c r="W369" s="5" t="n">
-        <v>-38.4680372</v>
+        <v>-38.467952</v>
       </c>
     </row>
     <row r="370" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30277,10 +30521,10 @@
         <v>1716</v>
       </c>
       <c r="V370" s="5" t="n">
-        <v>-3.7746642</v>
+        <v>-3.774664</v>
       </c>
       <c r="W370" s="5" t="n">
-        <v>-38.5861864</v>
+        <v>-38.586186</v>
       </c>
     </row>
     <row r="371" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30338,10 +30582,10 @@
         <v>1720</v>
       </c>
       <c r="V371" s="5" t="n">
-        <v>-3.8324924</v>
+        <v>-3.823604</v>
       </c>
       <c r="W371" s="5" t="n">
-        <v>-38.559215</v>
+        <v>-38.555759</v>
       </c>
     </row>
     <row r="372" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30397,10 +30641,10 @@
         <v>1725</v>
       </c>
       <c r="V372" s="5" t="n">
-        <v>-3.8009865</v>
+        <v>-3.800967</v>
       </c>
       <c r="W372" s="5" t="n">
-        <v>-38.5771249</v>
+        <v>-38.577036</v>
       </c>
     </row>
     <row r="373" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30456,10 +30700,10 @@
         <v>1729</v>
       </c>
       <c r="V373" s="5" t="n">
-        <v>-3.8106692</v>
+        <v>-3.810952</v>
       </c>
       <c r="W373" s="5" t="n">
-        <v>-38.5829388</v>
+        <v>-38.584066</v>
       </c>
     </row>
     <row r="374" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30514,8 +30758,12 @@
       <c r="U374" s="5" t="s">
         <v>1733</v>
       </c>
-      <c r="V374" s="5"/>
-      <c r="W374" s="5"/>
+      <c r="V374" s="5" t="n">
+        <v>-3.801694</v>
+      </c>
+      <c r="W374" s="5" t="n">
+        <v>-38.544442</v>
+      </c>
     </row>
     <row r="375" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A375" s="5" t="s">
@@ -30570,10 +30818,10 @@
         <v>1737</v>
       </c>
       <c r="V375" s="5" t="n">
-        <v>-3.8288186</v>
+        <v>-3.831058</v>
       </c>
       <c r="W375" s="5" t="n">
-        <v>-38.4801655</v>
+        <v>-38.480192</v>
       </c>
     </row>
     <row r="376" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30629,10 +30877,10 @@
         <v>1741</v>
       </c>
       <c r="V376" s="5" t="n">
-        <v>-3.8254927</v>
+        <v>-3.825532</v>
       </c>
       <c r="W376" s="5" t="n">
-        <v>-38.4854463</v>
+        <v>-38.485446</v>
       </c>
     </row>
     <row r="377" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30688,10 +30936,10 @@
         <v>1745</v>
       </c>
       <c r="V377" s="5" t="n">
-        <v>-3.8215821</v>
+        <v>-3.821582</v>
       </c>
       <c r="W377" s="5" t="n">
-        <v>-38.4724607</v>
+        <v>-38.472461</v>
       </c>
     </row>
     <row r="378" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30748,8 +30996,12 @@
       <c r="U378" s="5" t="s">
         <v>1749</v>
       </c>
-      <c r="V378" s="5"/>
-      <c r="W378" s="5"/>
+      <c r="V378" s="5" t="n">
+        <v>-3.825678</v>
+      </c>
+      <c r="W378" s="5" t="n">
+        <v>-38.57659</v>
+      </c>
     </row>
     <row r="379" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A379" s="5" t="s">
@@ -30806,10 +31058,10 @@
         <v>1753</v>
       </c>
       <c r="V379" s="5" t="n">
-        <v>-3.7203046</v>
+        <v>-3.7208</v>
       </c>
       <c r="W379" s="5" t="n">
-        <v>-38.5723699</v>
+        <v>-38.571836</v>
       </c>
     </row>
     <row r="380" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30867,10 +31119,10 @@
         <v>1757</v>
       </c>
       <c r="V380" s="5" t="n">
-        <v>-3.8264244</v>
+        <v>-3.826633</v>
       </c>
       <c r="W380" s="5" t="n">
-        <v>-38.5561454</v>
+        <v>-38.554954</v>
       </c>
     </row>
     <row r="381" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30926,10 +31178,10 @@
         <v>1761</v>
       </c>
       <c r="V381" s="5" t="n">
-        <v>-3.7903371</v>
+        <v>-3.79063</v>
       </c>
       <c r="W381" s="5" t="n">
-        <v>-38.6247232</v>
+        <v>-38.624774</v>
       </c>
     </row>
     <row r="382" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -30987,10 +31239,10 @@
         <v>1765</v>
       </c>
       <c r="V382" s="5" t="n">
-        <v>-3.7086481</v>
+        <v>-3.708688</v>
       </c>
       <c r="W382" s="5" t="n">
-        <v>-38.5700283</v>
+        <v>-38.569916</v>
       </c>
     </row>
     <row r="383" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31052,10 +31304,10 @@
         <v>1769</v>
       </c>
       <c r="V383" s="5" t="n">
-        <v>-3.8353628</v>
+        <v>-3.835344</v>
       </c>
       <c r="W383" s="5" t="n">
-        <v>-38.5750351</v>
+        <v>-38.575026</v>
       </c>
     </row>
     <row r="384" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31113,10 +31365,10 @@
         <v>1773</v>
       </c>
       <c r="V384" s="5" t="n">
-        <v>-3.7799233</v>
+        <v>-3.780082</v>
       </c>
       <c r="W384" s="5" t="n">
-        <v>-38.589627</v>
+        <v>-38.589801</v>
       </c>
     </row>
     <row r="385" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31172,10 +31424,10 @@
         <v>503</v>
       </c>
       <c r="V385" s="5" t="n">
-        <v>-3.7005049</v>
+        <v>-3.700496</v>
       </c>
       <c r="W385" s="5" t="n">
-        <v>-38.5856701</v>
+        <v>-38.58579</v>
       </c>
     </row>
     <row r="386" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31233,10 +31485,10 @@
         <v>1779</v>
       </c>
       <c r="V386" s="5" t="n">
-        <v>-3.786443</v>
+        <v>-3.786327</v>
       </c>
       <c r="W386" s="5" t="n">
-        <v>-38.6105283</v>
+        <v>-38.610488</v>
       </c>
     </row>
     <row r="387" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31294,10 +31546,10 @@
         <v>1783</v>
       </c>
       <c r="V387" s="5" t="n">
-        <v>-3.7766002</v>
+        <v>-3.776647</v>
       </c>
       <c r="W387" s="5" t="n">
-        <v>-38.5777456</v>
+        <v>-38.577779</v>
       </c>
     </row>
     <row r="388" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31353,10 +31605,10 @@
         <v>1787</v>
       </c>
       <c r="V388" s="5" t="n">
-        <v>-3.7058439</v>
+        <v>-3.705801</v>
       </c>
       <c r="W388" s="5" t="n">
-        <v>-38.5897694</v>
+        <v>-38.589792</v>
       </c>
     </row>
     <row r="389" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31412,10 +31664,10 @@
         <v>1791</v>
       </c>
       <c r="V389" s="5" t="n">
-        <v>-3.7048643</v>
+        <v>-3.704658</v>
       </c>
       <c r="W389" s="5" t="n">
-        <v>-38.5896511</v>
+        <v>-38.589481</v>
       </c>
     </row>
     <row r="390" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31471,10 +31723,10 @@
         <v>1795</v>
       </c>
       <c r="V390" s="5" t="n">
-        <v>-3.7910322</v>
+        <v>-3.790818</v>
       </c>
       <c r="W390" s="5" t="n">
-        <v>-38.4752121</v>
+        <v>-38.475474</v>
       </c>
     </row>
     <row r="391" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31530,10 +31782,10 @@
         <v>1799</v>
       </c>
       <c r="V391" s="5" t="n">
-        <v>-3.7257202</v>
+        <v>-3.725696</v>
       </c>
       <c r="W391" s="5" t="n">
-        <v>-38.5729164</v>
+        <v>-38.572928</v>
       </c>
     </row>
     <row r="392" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31589,10 +31841,10 @@
         <v>1803</v>
       </c>
       <c r="V392" s="5" t="n">
-        <v>-3.8264129</v>
+        <v>-3.826529</v>
       </c>
       <c r="W392" s="5" t="n">
-        <v>-38.5648874</v>
+        <v>-38.564929</v>
       </c>
     </row>
     <row r="393" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31647,8 +31899,12 @@
       <c r="U393" s="5" t="s">
         <v>1807</v>
       </c>
-      <c r="V393" s="5"/>
-      <c r="W393" s="5"/>
+      <c r="V393" s="5" t="n">
+        <v>-3.82245</v>
+      </c>
+      <c r="W393" s="5" t="n">
+        <v>-38.471147</v>
+      </c>
     </row>
     <row r="394" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A394" s="5" t="s">
@@ -31702,8 +31958,12 @@
       <c r="U394" s="5" t="s">
         <v>1812</v>
       </c>
-      <c r="V394" s="5"/>
-      <c r="W394" s="5"/>
+      <c r="V394" s="5" t="n">
+        <v>-3.784099</v>
+      </c>
+      <c r="W394" s="5" t="n">
+        <v>-38.503545</v>
+      </c>
     </row>
     <row r="395" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A395" s="5" t="s">
@@ -31758,10 +32018,10 @@
         <v>1816</v>
       </c>
       <c r="V395" s="5" t="n">
-        <v>-3.8363837</v>
+        <v>-3.836374</v>
       </c>
       <c r="W395" s="5" t="n">
-        <v>-38.5759545</v>
+        <v>-38.575999</v>
       </c>
     </row>
     <row r="396" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31817,10 +32077,10 @@
         <v>1820</v>
       </c>
       <c r="V396" s="5" t="n">
-        <v>-3.8328368</v>
+        <v>-3.830367</v>
       </c>
       <c r="W396" s="5" t="n">
-        <v>-38.5917897</v>
+        <v>-38.590477</v>
       </c>
     </row>
     <row r="397" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31876,10 +32136,10 @@
         <v>1824</v>
       </c>
       <c r="V397" s="5" t="n">
-        <v>-3.7371626</v>
+        <v>-3.737157</v>
       </c>
       <c r="W397" s="5" t="n">
-        <v>-38.5990555</v>
+        <v>-38.599255</v>
       </c>
     </row>
     <row r="398" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31937,10 +32197,10 @@
         <v>98</v>
       </c>
       <c r="V398" s="5" t="n">
-        <v>-3.7640916</v>
+        <v>-3.763969</v>
       </c>
       <c r="W398" s="5" t="n">
-        <v>-38.563127</v>
+        <v>-38.563171</v>
       </c>
     </row>
     <row r="399" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -31996,10 +32256,10 @@
         <v>1830</v>
       </c>
       <c r="V399" s="5" t="n">
-        <v>-3.726389</v>
+        <v>-3.726486</v>
       </c>
       <c r="W399" s="5" t="n">
-        <v>-38.4657627</v>
+        <v>-38.465718</v>
       </c>
     </row>
     <row r="400" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32054,8 +32314,12 @@
       <c r="U400" s="5" t="s">
         <v>1835</v>
       </c>
-      <c r="V400" s="5"/>
-      <c r="W400" s="5"/>
+      <c r="V400" s="5" t="n">
+        <v>-3.787577</v>
+      </c>
+      <c r="W400" s="5" t="n">
+        <v>-38.509349</v>
+      </c>
     </row>
     <row r="401" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A401" s="5" t="s">
@@ -32110,10 +32374,10 @@
         <v>1839</v>
       </c>
       <c r="V401" s="5" t="n">
-        <v>-3.7757693</v>
+        <v>-3.775631</v>
       </c>
       <c r="W401" s="5" t="n">
-        <v>-38.588189</v>
+        <v>-38.588167</v>
       </c>
     </row>
     <row r="402" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32173,10 +32437,10 @@
         <v>1844</v>
       </c>
       <c r="V402" s="5" t="n">
-        <v>-3.7319389</v>
+        <v>-3.731503</v>
       </c>
       <c r="W402" s="5" t="n">
-        <v>-38.5892764</v>
+        <v>-38.58902</v>
       </c>
     </row>
     <row r="403" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32234,10 +32498,10 @@
         <v>1848</v>
       </c>
       <c r="V403" s="5" t="n">
-        <v>-3.786544</v>
+        <v>-3.786514</v>
       </c>
       <c r="W403" s="5" t="n">
-        <v>-38.5936488</v>
+        <v>-38.59378</v>
       </c>
     </row>
     <row r="404" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32295,10 +32559,10 @@
         <v>1852</v>
       </c>
       <c r="V404" s="5" t="n">
-        <v>-3.7636949</v>
+        <v>-3.762732</v>
       </c>
       <c r="W404" s="5" t="n">
-        <v>-38.5997292</v>
+        <v>-38.59988</v>
       </c>
     </row>
     <row r="405" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32354,10 +32618,10 @@
         <v>1856</v>
       </c>
       <c r="V405" s="5" t="n">
-        <v>-3.8534114</v>
+        <v>-3.853428</v>
       </c>
       <c r="W405" s="5" t="n">
-        <v>-38.5007913</v>
+        <v>-38.500772</v>
       </c>
     </row>
     <row r="406" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32416,7 +32680,7 @@
         <v>-3.718072</v>
       </c>
       <c r="W406" s="5" t="n">
-        <v>-38.4653616</v>
+        <v>-38.465362</v>
       </c>
     </row>
     <row r="407" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32478,10 +32742,10 @@
         <v>1863</v>
       </c>
       <c r="V407" s="5" t="n">
-        <v>-3.7496758</v>
+        <v>-3.754897</v>
       </c>
       <c r="W407" s="5" t="n">
-        <v>-38.6022659</v>
+        <v>-38.603022</v>
       </c>
     </row>
     <row r="408" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32537,10 +32801,10 @@
         <v>1867</v>
       </c>
       <c r="V408" s="5" t="n">
-        <v>-3.7540967</v>
+        <v>-3.754122</v>
       </c>
       <c r="W408" s="5" t="n">
-        <v>-38.5400403</v>
+        <v>-38.540045</v>
       </c>
     </row>
     <row r="409" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32596,10 +32860,10 @@
         <v>1871</v>
       </c>
       <c r="V409" s="5" t="n">
-        <v>-3.7198524</v>
+        <v>-3.719736</v>
       </c>
       <c r="W409" s="5" t="n">
-        <v>-38.5831457</v>
+        <v>-38.583379</v>
       </c>
     </row>
     <row r="410" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32655,10 +32919,10 @@
         <v>1875</v>
       </c>
       <c r="V410" s="5" t="n">
-        <v>-3.7743301</v>
+        <v>-3.773604</v>
       </c>
       <c r="W410" s="5" t="n">
-        <v>-38.6089415</v>
+        <v>-38.613924</v>
       </c>
     </row>
     <row r="411" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32714,10 +32978,10 @@
         <v>646</v>
       </c>
       <c r="V411" s="5" t="n">
-        <v>-3.7712235</v>
+        <v>-3.771224</v>
       </c>
       <c r="W411" s="5" t="n">
-        <v>-38.5157565</v>
+        <v>-38.515757</v>
       </c>
     </row>
     <row r="412" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32773,10 +33037,10 @@
         <v>1881</v>
       </c>
       <c r="V412" s="5" t="n">
-        <v>-3.7969321</v>
+        <v>-3.797241</v>
       </c>
       <c r="W412" s="5" t="n">
-        <v>-38.6038699</v>
+        <v>-38.608005</v>
       </c>
     </row>
     <row r="413" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32834,10 +33098,10 @@
         <v>1885</v>
       </c>
       <c r="V413" s="5" t="n">
-        <v>-3.7490914</v>
+        <v>-3.749091</v>
       </c>
       <c r="W413" s="5" t="n">
-        <v>-38.5698192</v>
+        <v>-38.569819</v>
       </c>
     </row>
     <row r="414" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32897,10 +33161,10 @@
         <v>1889</v>
       </c>
       <c r="V414" s="5" t="n">
-        <v>-3.8135021</v>
+        <v>-3.813726</v>
       </c>
       <c r="W414" s="5" t="n">
-        <v>-38.5377511</v>
+        <v>-38.537468</v>
       </c>
     </row>
     <row r="415" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32956,10 +33220,10 @@
         <v>1893</v>
       </c>
       <c r="V415" s="5" t="n">
-        <v>-3.8054226</v>
+        <v>-3.805498</v>
       </c>
       <c r="W415" s="5" t="n">
-        <v>-38.623146</v>
+        <v>-38.623199</v>
       </c>
     </row>
     <row r="416" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33017,10 +33281,10 @@
         <v>1897</v>
       </c>
       <c r="V416" s="5" t="n">
-        <v>-3.8192071</v>
+        <v>-3.819118</v>
       </c>
       <c r="W416" s="5" t="n">
-        <v>-38.5064888</v>
+        <v>-38.506437</v>
       </c>
     </row>
     <row r="417" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33076,10 +33340,10 @@
         <v>1901</v>
       </c>
       <c r="V417" s="5" t="n">
-        <v>-3.7886846</v>
+        <v>-3.792827</v>
       </c>
       <c r="W417" s="5" t="n">
-        <v>-38.5172944</v>
+        <v>-38.518715</v>
       </c>
     </row>
     <row r="418" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33137,10 +33401,10 @@
         <v>1905</v>
       </c>
       <c r="V418" s="5" t="n">
-        <v>-3.8235117</v>
+        <v>-3.82251</v>
       </c>
       <c r="W418" s="5" t="n">
-        <v>-38.4827463</v>
+        <v>-38.487478</v>
       </c>
     </row>
     <row r="419" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33198,10 +33462,10 @@
         <v>1910</v>
       </c>
       <c r="V419" s="5" t="n">
-        <v>-3.8223236</v>
+        <v>-3.822515</v>
       </c>
       <c r="W419" s="5" t="n">
-        <v>-38.4777216</v>
+        <v>-38.477667</v>
       </c>
     </row>
     <row r="420" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33257,10 +33521,10 @@
         <v>361</v>
       </c>
       <c r="V420" s="5" t="n">
-        <v>-3.827182</v>
+        <v>-3.826706</v>
       </c>
       <c r="W420" s="5" t="n">
-        <v>-38.4639405</v>
+        <v>-38.463958</v>
       </c>
     </row>
     <row r="421" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33316,10 +33580,10 @@
         <v>1916</v>
       </c>
       <c r="V421" s="5" t="n">
-        <v>-3.8310386</v>
+        <v>-3.831297</v>
       </c>
       <c r="W421" s="5" t="n">
-        <v>-38.5239655</v>
+        <v>-38.523832</v>
       </c>
     </row>
     <row r="422" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33380,8 +33644,12 @@
       <c r="U422" s="5" t="s">
         <v>1921</v>
       </c>
-      <c r="V422" s="5"/>
-      <c r="W422" s="5"/>
+      <c r="V422" s="5" t="n">
+        <v>-3.722208</v>
+      </c>
+      <c r="W422" s="5" t="n">
+        <v>-38.590759</v>
+      </c>
     </row>
     <row r="423" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A423" s="5" t="s">
@@ -33436,10 +33704,10 @@
         <v>1925</v>
       </c>
       <c r="V423" s="5" t="n">
-        <v>-3.7933959</v>
+        <v>-3.791233</v>
       </c>
       <c r="W423" s="5" t="n">
-        <v>-38.6137736</v>
+        <v>-38.619158</v>
       </c>
     </row>
     <row r="424" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33507,10 +33775,10 @@
         <v>1932</v>
       </c>
       <c r="V424" s="5" t="n">
-        <v>-3.8174476</v>
+        <v>-3.817428</v>
       </c>
       <c r="W424" s="5" t="n">
-        <v>-38.5223302</v>
+        <v>-38.522263</v>
       </c>
     </row>
     <row r="425" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33567,8 +33835,12 @@
       <c r="U425" s="5" t="s">
         <v>1936</v>
       </c>
-      <c r="V425" s="5"/>
-      <c r="W425" s="5"/>
+      <c r="V425" s="5" t="n">
+        <v>-3.819837</v>
+      </c>
+      <c r="W425" s="5" t="n">
+        <v>-38.514852</v>
+      </c>
     </row>
     <row r="426" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A426" s="5" t="s">
@@ -33623,10 +33895,10 @@
         <v>1940</v>
       </c>
       <c r="V426" s="5" t="n">
-        <v>-3.7977264</v>
+        <v>-3.797747</v>
       </c>
       <c r="W426" s="5" t="n">
-        <v>-38.5117301</v>
+        <v>-38.511726</v>
       </c>
     </row>
     <row r="427" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33683,8 +33955,12 @@
       <c r="U427" s="5" t="s">
         <v>1944</v>
       </c>
-      <c r="V427" s="5"/>
-      <c r="W427" s="5"/>
+      <c r="V427" s="5" t="n">
+        <v>-3.854599</v>
+      </c>
+      <c r="W427" s="5" t="n">
+        <v>-38.519031</v>
+      </c>
     </row>
     <row r="428" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A428" s="5" t="s">
@@ -33739,10 +34015,10 @@
         <v>1948</v>
       </c>
       <c r="V428" s="5" t="n">
-        <v>-3.7817183</v>
+        <v>-3.781718</v>
       </c>
       <c r="W428" s="5" t="n">
-        <v>-38.6243692</v>
+        <v>-38.624369</v>
       </c>
     </row>
     <row r="429" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33798,10 +34074,10 @@
         <v>1953</v>
       </c>
       <c r="V429" s="5" t="n">
-        <v>-3.7954292</v>
+        <v>-3.795429</v>
       </c>
       <c r="W429" s="5" t="n">
-        <v>-38.5843179</v>
+        <v>-38.584318</v>
       </c>
     </row>
     <row r="430" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33857,10 +34133,10 @@
         <v>1957</v>
       </c>
       <c r="V430" s="5" t="n">
-        <v>-3.7608608</v>
+        <v>-3.760847</v>
       </c>
       <c r="W430" s="5" t="n">
-        <v>-38.6031116</v>
+        <v>-38.603206</v>
       </c>
     </row>
     <row r="431" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33920,10 +34196,10 @@
         <v>1961</v>
       </c>
       <c r="V431" s="5" t="n">
-        <v>-3.7634547</v>
+        <v>-3.763587</v>
       </c>
       <c r="W431" s="5" t="n">
-        <v>-38.5341285</v>
+        <v>-38.533985</v>
       </c>
     </row>
     <row r="432" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -33981,10 +34257,10 @@
         <v>1965</v>
       </c>
       <c r="V432" s="5" t="n">
-        <v>-3.8564703</v>
+        <v>-3.855735</v>
       </c>
       <c r="W432" s="5" t="n">
-        <v>-38.5143561</v>
+        <v>-38.51454</v>
       </c>
     </row>
     <row r="433" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34040,10 +34316,10 @@
         <v>466</v>
       </c>
       <c r="V433" s="5" t="n">
-        <v>-3.7887918</v>
+        <v>-3.788339</v>
       </c>
       <c r="W433" s="5" t="n">
-        <v>-38.6104083</v>
+        <v>-38.609833</v>
       </c>
     </row>
     <row r="434" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34100,8 +34376,12 @@
       <c r="U434" s="5" t="s">
         <v>1971</v>
       </c>
-      <c r="V434" s="5"/>
-      <c r="W434" s="5"/>
+      <c r="V434" s="5" t="n">
+        <v>-3.877098</v>
+      </c>
+      <c r="W434" s="5" t="n">
+        <v>-38.515756</v>
+      </c>
     </row>
     <row r="435" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A435" s="5" t="s">
@@ -34160,10 +34440,10 @@
         <v>1975</v>
       </c>
       <c r="V435" s="5" t="n">
-        <v>-3.7727052</v>
+        <v>-3.772653</v>
       </c>
       <c r="W435" s="5" t="n">
-        <v>-38.5586214</v>
+        <v>-38.55889</v>
       </c>
     </row>
     <row r="436" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34219,10 +34499,10 @@
         <v>1979</v>
       </c>
       <c r="V436" s="5" t="n">
-        <v>-3.791557</v>
+        <v>-3.79172</v>
       </c>
       <c r="W436" s="5" t="n">
-        <v>-38.5371088</v>
+        <v>-38.537578</v>
       </c>
     </row>
     <row r="437" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34278,10 +34558,10 @@
         <v>1983</v>
       </c>
       <c r="V437" s="5" t="n">
-        <v>-3.8209383</v>
+        <v>-3.820907</v>
       </c>
       <c r="W437" s="5" t="n">
-        <v>-38.4892911</v>
+        <v>-38.48928</v>
       </c>
     </row>
     <row r="438" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34337,10 +34617,10 @@
         <v>1987</v>
       </c>
       <c r="V438" s="5" t="n">
-        <v>-3.7829704</v>
+        <v>-3.788982</v>
       </c>
       <c r="W438" s="5" t="n">
-        <v>-38.6275377</v>
+        <v>-38.629516</v>
       </c>
     </row>
     <row r="439" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34396,10 +34676,10 @@
         <v>293</v>
       </c>
       <c r="V439" s="5" t="n">
-        <v>-3.7561705</v>
+        <v>-3.756435</v>
       </c>
       <c r="W439" s="5" t="n">
-        <v>-38.5921377</v>
+        <v>-38.592178</v>
       </c>
     </row>
     <row r="440" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34455,10 +34735,10 @@
         <v>1993</v>
       </c>
       <c r="V440" s="5" t="n">
-        <v>-3.8285946</v>
+        <v>-3.828597</v>
       </c>
       <c r="W440" s="5" t="n">
-        <v>-38.4862578</v>
+        <v>-38.486277</v>
       </c>
     </row>
     <row r="441" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34514,10 +34794,10 @@
         <v>86</v>
       </c>
       <c r="V441" s="5" t="n">
-        <v>-3.7925828</v>
+        <v>-3.79295</v>
       </c>
       <c r="W441" s="5" t="n">
-        <v>-38.6257333</v>
+        <v>-38.624636</v>
       </c>
     </row>
     <row r="442" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34574,8 +34854,12 @@
       <c r="U442" s="5" t="s">
         <v>2000</v>
       </c>
-      <c r="V442" s="5"/>
-      <c r="W442" s="5"/>
+      <c r="V442" s="5" t="n">
+        <v>-3.831286</v>
+      </c>
+      <c r="W442" s="5" t="n">
+        <v>-38.555995</v>
+      </c>
     </row>
     <row r="443" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A443" s="5" t="s">
@@ -34630,10 +34914,10 @@
         <v>2004</v>
       </c>
       <c r="V443" s="5" t="n">
-        <v>-3.7814629</v>
+        <v>-3.781494</v>
       </c>
       <c r="W443" s="5" t="n">
-        <v>-38.6029275</v>
+        <v>-38.60301</v>
       </c>
     </row>
     <row r="444" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34689,10 +34973,10 @@
         <v>2008</v>
       </c>
       <c r="V444" s="5" t="n">
-        <v>-3.8458702</v>
+        <v>-3.845365</v>
       </c>
       <c r="W444" s="5" t="n">
-        <v>-38.5232128</v>
+        <v>-38.523363</v>
       </c>
     </row>
     <row r="445" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34748,10 +35032,10 @@
         <v>2012</v>
       </c>
       <c r="V445" s="5" t="n">
-        <v>-3.8064991</v>
+        <v>-3.806393</v>
       </c>
       <c r="W445" s="5" t="n">
-        <v>-38.5686999</v>
+        <v>-38.568523</v>
       </c>
     </row>
     <row r="446" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34807,10 +35091,10 @@
         <v>2016</v>
       </c>
       <c r="V446" s="5" t="n">
-        <v>-3.7122631</v>
+        <v>-3.712135</v>
       </c>
       <c r="W446" s="5" t="n">
-        <v>-38.5556224</v>
+        <v>-38.555565</v>
       </c>
     </row>
     <row r="447" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34866,10 +35150,10 @@
         <v>2020</v>
       </c>
       <c r="V447" s="5" t="n">
-        <v>-3.713154</v>
+        <v>-3.712634</v>
       </c>
       <c r="W447" s="5" t="n">
-        <v>-38.5914862</v>
+        <v>-38.592069</v>
       </c>
     </row>
     <row r="448" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34925,10 +35209,10 @@
         <v>2024</v>
       </c>
       <c r="V448" s="5" t="n">
-        <v>-3.7987461</v>
+        <v>-3.798654</v>
       </c>
       <c r="W448" s="5" t="n">
-        <v>-38.6018498</v>
+        <v>-38.601849</v>
       </c>
     </row>
     <row r="449" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -34984,10 +35268,10 @@
         <v>2028</v>
       </c>
       <c r="V449" s="5" t="n">
-        <v>-3.7707228</v>
+        <v>-3.770738</v>
       </c>
       <c r="W449" s="5" t="n">
-        <v>-38.6136614</v>
+        <v>-38.613738</v>
       </c>
     </row>
     <row r="450" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35042,8 +35326,12 @@
       <c r="U450" s="5" t="s">
         <v>2032</v>
       </c>
-      <c r="V450" s="5"/>
-      <c r="W450" s="5"/>
+      <c r="V450" s="5" t="n">
+        <v>-3.824241</v>
+      </c>
+      <c r="W450" s="5" t="n">
+        <v>-38.519202</v>
+      </c>
     </row>
     <row r="451" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A451" s="5" t="s">
@@ -35099,8 +35387,12 @@
       <c r="U451" s="5" t="s">
         <v>2036</v>
       </c>
-      <c r="V451" s="5"/>
-      <c r="W451" s="5"/>
+      <c r="V451" s="5" t="n">
+        <v>-3.877576</v>
+      </c>
+      <c r="W451" s="5" t="n">
+        <v>-38.515215</v>
+      </c>
     </row>
     <row r="452" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A452" s="5" t="s">
@@ -35165,10 +35457,10 @@
         <v>273</v>
       </c>
       <c r="V452" s="5" t="n">
-        <v>-3.7644943</v>
+        <v>-3.764494</v>
       </c>
       <c r="W452" s="5" t="n">
-        <v>-38.5878033</v>
+        <v>-38.587803</v>
       </c>
     </row>
     <row r="453" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35230,10 +35522,10 @@
         <v>2046</v>
       </c>
       <c r="V453" s="5" t="n">
-        <v>-3.7571294</v>
+        <v>-3.757129</v>
       </c>
       <c r="W453" s="5" t="n">
-        <v>-38.5717866</v>
+        <v>-38.571787</v>
       </c>
     </row>
     <row r="454" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35288,8 +35580,12 @@
       <c r="U454" s="5" t="s">
         <v>2051</v>
       </c>
-      <c r="V454" s="5"/>
-      <c r="W454" s="5"/>
+      <c r="V454" s="5" t="n">
+        <v>-3.818897</v>
+      </c>
+      <c r="W454" s="5" t="n">
+        <v>-38.591632</v>
+      </c>
     </row>
     <row r="455" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A455" s="5" t="s">
@@ -35344,10 +35640,10 @@
         <v>2055</v>
       </c>
       <c r="V455" s="5" t="n">
-        <v>-3.7937133</v>
+        <v>-3.794495</v>
       </c>
       <c r="W455" s="5" t="n">
-        <v>-38.55335</v>
+        <v>-38.554162</v>
       </c>
     </row>
     <row r="456" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35403,10 +35699,10 @@
         <v>2059</v>
       </c>
       <c r="V456" s="5" t="n">
-        <v>-3.7870457</v>
+        <v>-3.797503</v>
       </c>
       <c r="W456" s="5" t="n">
-        <v>-38.4678883</v>
+        <v>-38.467267</v>
       </c>
     </row>
     <row r="457" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35464,10 +35760,10 @@
         <v>2063</v>
       </c>
       <c r="V457" s="5" t="n">
-        <v>-3.7148126</v>
+        <v>-3.713232</v>
       </c>
       <c r="W457" s="5" t="n">
-        <v>-38.5446166</v>
+        <v>-38.545722</v>
       </c>
     </row>
     <row r="458" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35523,10 +35819,10 @@
         <v>2067</v>
       </c>
       <c r="V458" s="5" t="n">
-        <v>-3.7596449</v>
+        <v>-3.759637</v>
       </c>
       <c r="W458" s="5" t="n">
-        <v>-38.5168221</v>
+        <v>-38.5168</v>
       </c>
     </row>
     <row r="459" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35582,10 +35878,10 @@
         <v>219</v>
       </c>
       <c r="V459" s="5" t="n">
-        <v>-3.783015</v>
+        <v>-3.783053</v>
       </c>
       <c r="W459" s="5" t="n">
-        <v>-38.5424879</v>
+        <v>-38.542612</v>
       </c>
     </row>
     <row r="460" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35643,10 +35939,10 @@
         <v>2073</v>
       </c>
       <c r="V460" s="5" t="n">
-        <v>-3.7913559</v>
+        <v>-3.791356</v>
       </c>
       <c r="W460" s="5" t="n">
-        <v>-38.4765393</v>
+        <v>-38.476539</v>
       </c>
     </row>
     <row r="461" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35702,10 +35998,10 @@
         <v>2077</v>
       </c>
       <c r="V461" s="5" t="n">
-        <v>-3.8143839</v>
+        <v>-3.814384</v>
       </c>
       <c r="W461" s="5" t="n">
-        <v>-38.4661585</v>
+        <v>-38.466159</v>
       </c>
     </row>
     <row r="462" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35760,8 +36056,12 @@
       <c r="U462" s="5" t="s">
         <v>2081</v>
       </c>
-      <c r="V462" s="5"/>
-      <c r="W462" s="5"/>
+      <c r="V462" s="5" t="n">
+        <v>-3.801917</v>
+      </c>
+      <c r="W462" s="5" t="n">
+        <v>-38.61435</v>
+      </c>
     </row>
     <row r="463" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A463" s="5" t="s">
@@ -35817,8 +36117,12 @@
       <c r="U463" s="5" t="s">
         <v>2085</v>
       </c>
-      <c r="V463" s="5"/>
-      <c r="W463" s="5"/>
+      <c r="V463" s="5" t="n">
+        <v>-3.848334</v>
+      </c>
+      <c r="W463" s="5" t="n">
+        <v>-38.520216</v>
+      </c>
     </row>
     <row r="464" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A464" s="5" t="s">
@@ -35875,10 +36179,10 @@
         <v>2090</v>
       </c>
       <c r="V464" s="5" t="n">
-        <v>-3.862985</v>
+        <v>-3.861598</v>
       </c>
       <c r="W464" s="5" t="n">
-        <v>-38.5073441</v>
+        <v>-38.505796</v>
       </c>
     </row>
     <row r="465" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35936,10 +36240,10 @@
         <v>2094</v>
       </c>
       <c r="V465" s="5" t="n">
-        <v>-3.7811801</v>
+        <v>-3.781068</v>
       </c>
       <c r="W465" s="5" t="n">
-        <v>-38.6016506</v>
+        <v>-38.601326</v>
       </c>
     </row>
     <row r="466" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -35995,10 +36299,10 @@
         <v>2098</v>
       </c>
       <c r="V466" s="5" t="n">
-        <v>-3.7996623</v>
+        <v>-3.799557</v>
       </c>
       <c r="W466" s="5" t="n">
-        <v>-38.5284703</v>
+        <v>-38.528556</v>
       </c>
     </row>
     <row r="467" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36055,8 +36359,12 @@
       <c r="U467" s="5" t="s">
         <v>2102</v>
       </c>
-      <c r="V467" s="5"/>
-      <c r="W467" s="5"/>
+      <c r="V467" s="5" t="n">
+        <v>-3.832786</v>
+      </c>
+      <c r="W467" s="5" t="n">
+        <v>-38.585793</v>
+      </c>
     </row>
     <row r="468" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A468" s="5" t="s">
@@ -36111,10 +36419,10 @@
         <v>2106</v>
       </c>
       <c r="V468" s="5" t="n">
-        <v>-3.7763677</v>
+        <v>-3.775721</v>
       </c>
       <c r="W468" s="5" t="n">
-        <v>-38.558918</v>
+        <v>-38.558933</v>
       </c>
     </row>
     <row r="469" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36172,10 +36480,10 @@
         <v>2110</v>
       </c>
       <c r="V469" s="5" t="n">
-        <v>-3.8610067</v>
+        <v>-3.858703</v>
       </c>
       <c r="W469" s="5" t="n">
-        <v>-38.4929316</v>
+        <v>-38.492768</v>
       </c>
     </row>
     <row r="470" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36230,8 +36538,12 @@
       <c r="U470" s="5" t="s">
         <v>2114</v>
       </c>
-      <c r="V470" s="5"/>
-      <c r="W470" s="5"/>
+      <c r="V470" s="5" t="n">
+        <v>-3.788565</v>
+      </c>
+      <c r="W470" s="5" t="n">
+        <v>-38.527072</v>
+      </c>
     </row>
     <row r="471" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A471" s="5" t="s">
@@ -36288,10 +36600,10 @@
         <v>2118</v>
       </c>
       <c r="V471" s="5" t="n">
-        <v>-3.8390255</v>
+        <v>-3.839019</v>
       </c>
       <c r="W471" s="5" t="n">
-        <v>-38.5232798</v>
+        <v>-38.523131</v>
       </c>
     </row>
     <row r="472" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36346,8 +36658,12 @@
       <c r="U472" s="5" t="s">
         <v>2122</v>
       </c>
-      <c r="V472" s="5"/>
-      <c r="W472" s="5"/>
+      <c r="V472" s="5" t="n">
+        <v>-3.807674</v>
+      </c>
+      <c r="W472" s="5" t="n">
+        <v>-38.587579</v>
+      </c>
     </row>
     <row r="473" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A473" s="5" t="s">
@@ -36401,8 +36717,12 @@
       <c r="U473" s="5" t="s">
         <v>2126</v>
       </c>
-      <c r="V473" s="5"/>
-      <c r="W473" s="5"/>
+      <c r="V473" s="5" t="n">
+        <v>-3.852391</v>
+      </c>
+      <c r="W473" s="5" t="n">
+        <v>-38.511784</v>
+      </c>
     </row>
     <row r="474" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A474" s="5" t="s">
@@ -36462,7 +36782,7 @@
         <v>-3.848451</v>
       </c>
       <c r="W474" s="5" t="n">
-        <v>-38.5276338</v>
+        <v>-38.527634</v>
       </c>
     </row>
     <row r="475" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36518,10 +36838,10 @@
         <v>2134</v>
       </c>
       <c r="V475" s="5" t="n">
-        <v>-3.7171754</v>
+        <v>-3.717175</v>
       </c>
       <c r="W475" s="5" t="n">
-        <v>-38.5738972</v>
+        <v>-38.573897</v>
       </c>
     </row>
     <row r="476" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36577,10 +36897,10 @@
         <v>2138</v>
       </c>
       <c r="V476" s="5" t="n">
-        <v>-3.7940829</v>
+        <v>-3.794158</v>
       </c>
       <c r="W476" s="5" t="n">
-        <v>-38.5944367</v>
+        <v>-38.594438</v>
       </c>
     </row>
     <row r="477" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36642,10 +36962,10 @@
         <v>2143</v>
       </c>
       <c r="V477" s="5" t="n">
-        <v>-3.7168703</v>
+        <v>-3.71673</v>
       </c>
       <c r="W477" s="5" t="n">
-        <v>-38.5617764</v>
+        <v>-38.561684</v>
       </c>
     </row>
     <row r="478" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36701,10 +37021,10 @@
         <v>2147</v>
       </c>
       <c r="V478" s="5" t="n">
-        <v>-3.732959</v>
+        <v>-3.732945</v>
       </c>
       <c r="W478" s="5" t="n">
-        <v>-38.4825825</v>
+        <v>-38.482564</v>
       </c>
     </row>
     <row r="479" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36760,10 +37080,10 @@
         <v>2151</v>
       </c>
       <c r="V479" s="5" t="n">
-        <v>-3.7999194</v>
+        <v>-3.799919</v>
       </c>
       <c r="W479" s="5" t="n">
-        <v>-38.6009526</v>
+        <v>-38.600953</v>
       </c>
     </row>
     <row r="480" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36819,10 +37139,10 @@
         <v>108</v>
       </c>
       <c r="V480" s="5" t="n">
-        <v>-3.8310728</v>
+        <v>-3.831128</v>
       </c>
       <c r="W480" s="5" t="n">
-        <v>-38.5711175</v>
+        <v>-38.570701</v>
       </c>
     </row>
     <row r="481" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36878,10 +37198,10 @@
         <v>2157</v>
       </c>
       <c r="V481" s="5" t="n">
-        <v>-3.8114563</v>
+        <v>-3.807352</v>
       </c>
       <c r="W481" s="5" t="n">
-        <v>-38.6046601</v>
+        <v>-38.602108</v>
       </c>
     </row>
     <row r="482" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36937,10 +37257,10 @@
         <v>2161</v>
       </c>
       <c r="V482" s="5" t="n">
-        <v>-3.8272081</v>
+        <v>-3.819954</v>
       </c>
       <c r="W482" s="5" t="n">
-        <v>-38.4693926</v>
+        <v>-38.452228</v>
       </c>
     </row>
     <row r="483" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -36995,8 +37315,12 @@
       <c r="U483" s="5" t="s">
         <v>2165</v>
       </c>
-      <c r="V483" s="5"/>
-      <c r="W483" s="5"/>
+      <c r="V483" s="5" t="n">
+        <v>-3.821021</v>
+      </c>
+      <c r="W483" s="5" t="n">
+        <v>-38.608534</v>
+      </c>
     </row>
     <row r="484" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A484" s="5" t="s">
@@ -37052,8 +37376,12 @@
       <c r="U484" s="5" t="s">
         <v>2169</v>
       </c>
-      <c r="V484" s="5"/>
-      <c r="W484" s="5"/>
+      <c r="V484" s="5" t="n">
+        <v>-3.849679</v>
+      </c>
+      <c r="W484" s="5" t="n">
+        <v>-38.520696</v>
+      </c>
     </row>
     <row r="485" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A485" s="5" t="s">
@@ -37110,10 +37438,10 @@
         <v>1044</v>
       </c>
       <c r="V485" s="5" t="n">
-        <v>-3.8456721</v>
+        <v>-3.844662</v>
       </c>
       <c r="W485" s="5" t="n">
-        <v>-38.5068633</v>
+        <v>-38.506852</v>
       </c>
     </row>
     <row r="486" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37170,8 +37498,12 @@
       <c r="U486" s="5" t="s">
         <v>2175</v>
       </c>
-      <c r="V486" s="5"/>
-      <c r="W486" s="5"/>
+      <c r="V486" s="5" t="n">
+        <v>-3.823921</v>
+      </c>
+      <c r="W486" s="5" t="n">
+        <v>-38.514076</v>
+      </c>
     </row>
     <row r="487" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A487" s="5" t="s">
@@ -37232,10 +37564,10 @@
         <v>2180</v>
       </c>
       <c r="V487" s="5" t="n">
-        <v>-3.7545837</v>
+        <v>-3.757319</v>
       </c>
       <c r="W487" s="5" t="n">
-        <v>-38.5632679</v>
+        <v>-38.565339</v>
       </c>
     </row>
     <row r="488" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37291,10 +37623,10 @@
         <v>2185</v>
       </c>
       <c r="V488" s="5" t="n">
-        <v>-3.728877</v>
+        <v>-3.728842</v>
       </c>
       <c r="W488" s="5" t="n">
-        <v>-38.4853953</v>
+        <v>-38.485392</v>
       </c>
     </row>
     <row r="489" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37350,10 +37682,10 @@
         <v>2189</v>
       </c>
       <c r="V489" s="5" t="n">
-        <v>-3.8305988</v>
+        <v>-3.830615</v>
       </c>
       <c r="W489" s="5" t="n">
-        <v>-38.4919167</v>
+        <v>-38.491923</v>
       </c>
     </row>
     <row r="490" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37408,8 +37740,12 @@
       <c r="U490" s="5" t="s">
         <v>956</v>
       </c>
-      <c r="V490" s="5"/>
-      <c r="W490" s="5"/>
+      <c r="V490" s="5" t="n">
+        <v>-3.817308</v>
+      </c>
+      <c r="W490" s="5" t="n">
+        <v>-38.602224</v>
+      </c>
     </row>
     <row r="491" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A491" s="5" t="s">
@@ -37464,10 +37800,10 @@
         <v>2195</v>
       </c>
       <c r="V491" s="5" t="n">
-        <v>-3.7977151</v>
+        <v>-3.797705</v>
       </c>
       <c r="W491" s="5" t="n">
-        <v>-38.5809704</v>
+        <v>-38.580993</v>
       </c>
     </row>
     <row r="492" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37535,10 +37871,10 @@
         <v>2201</v>
       </c>
       <c r="V492" s="5" t="n">
-        <v>-3.8151672</v>
+        <v>-3.814959</v>
       </c>
       <c r="W492" s="5" t="n">
-        <v>-38.5102219</v>
+        <v>-38.509993</v>
       </c>
     </row>
     <row r="493" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37594,10 +37930,10 @@
         <v>2205</v>
       </c>
       <c r="V493" s="5" t="n">
-        <v>-3.8457373</v>
+        <v>-3.845737</v>
       </c>
       <c r="W493" s="5" t="n">
-        <v>-38.5230534</v>
+        <v>-38.523053</v>
       </c>
     </row>
     <row r="494" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37655,10 +37991,10 @@
         <v>2209</v>
       </c>
       <c r="V494" s="5" t="n">
-        <v>-3.8187537</v>
+        <v>-3.818793</v>
       </c>
       <c r="W494" s="5" t="n">
-        <v>-38.5580862</v>
+        <v>-38.558056</v>
       </c>
     </row>
     <row r="495" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37716,10 +38052,10 @@
         <v>2213</v>
       </c>
       <c r="V495" s="5" t="n">
-        <v>-3.7117731</v>
+        <v>-3.772702</v>
       </c>
       <c r="W495" s="5" t="n">
-        <v>-38.471838</v>
+        <v>-38.476879</v>
       </c>
     </row>
     <row r="496" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37775,10 +38111,10 @@
         <v>2217</v>
       </c>
       <c r="V496" s="5" t="n">
-        <v>-3.82634</v>
+        <v>-3.82612</v>
       </c>
       <c r="W496" s="5" t="n">
-        <v>-38.4775142</v>
+        <v>-38.477355</v>
       </c>
     </row>
     <row r="497" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37834,10 +38170,10 @@
         <v>2221</v>
       </c>
       <c r="V497" s="5" t="n">
-        <v>-3.7905233</v>
+        <v>-3.790523</v>
       </c>
       <c r="W497" s="5" t="n">
-        <v>-38.4664935</v>
+        <v>-38.466493</v>
       </c>
     </row>
     <row r="498" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37893,10 +38229,10 @@
         <v>251</v>
       </c>
       <c r="V498" s="5" t="n">
-        <v>-3.7091719</v>
+        <v>-3.709172</v>
       </c>
       <c r="W498" s="5" t="n">
-        <v>-38.5804059</v>
+        <v>-38.580406</v>
       </c>
     </row>
     <row r="499" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -37952,10 +38288,10 @@
         <v>2227</v>
       </c>
       <c r="V499" s="5" t="n">
-        <v>-3.8309566</v>
+        <v>-3.829393</v>
       </c>
       <c r="W499" s="5" t="n">
-        <v>-38.4673754</v>
+        <v>-38.466867</v>
       </c>
     </row>
     <row r="500" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38011,10 +38347,10 @@
         <v>1113</v>
       </c>
       <c r="V500" s="5" t="n">
-        <v>-3.7874942</v>
+        <v>-3.785873</v>
       </c>
       <c r="W500" s="5" t="n">
-        <v>-38.6014649</v>
+        <v>-38.605394</v>
       </c>
     </row>
     <row r="501" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38070,10 +38406,10 @@
         <v>2233</v>
       </c>
       <c r="V501" s="5" t="n">
-        <v>-3.8515049</v>
+        <v>-3.851326</v>
       </c>
       <c r="W501" s="5" t="n">
-        <v>-38.5020417</v>
+        <v>-38.50195</v>
       </c>
     </row>
     <row r="502" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38131,10 +38467,10 @@
         <v>2237</v>
       </c>
       <c r="V502" s="5" t="n">
-        <v>-3.7831251</v>
+        <v>-3.783156</v>
       </c>
       <c r="W502" s="5" t="n">
-        <v>-38.5028838</v>
+        <v>-38.502876</v>
       </c>
     </row>
     <row r="503" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38196,10 +38532,10 @@
         <v>2242</v>
       </c>
       <c r="V503" s="5" t="n">
-        <v>-3.7257183</v>
+        <v>-3.725663</v>
       </c>
       <c r="W503" s="5" t="n">
-        <v>-38.483869</v>
+        <v>-38.483831</v>
       </c>
     </row>
     <row r="504" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38255,10 +38591,10 @@
         <v>2246</v>
       </c>
       <c r="V504" s="5" t="n">
-        <v>-3.7558747</v>
+        <v>-3.755625</v>
       </c>
       <c r="W504" s="5" t="n">
-        <v>-38.5757626</v>
+        <v>-38.575137</v>
       </c>
     </row>
     <row r="505" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38316,10 +38652,10 @@
         <v>2250</v>
       </c>
       <c r="V505" s="5" t="n">
-        <v>-3.8312539</v>
+        <v>-3.831467</v>
       </c>
       <c r="W505" s="5" t="n">
-        <v>-38.5186666</v>
+        <v>-38.518746</v>
       </c>
     </row>
     <row r="506" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38374,8 +38710,12 @@
       <c r="U506" s="5" t="s">
         <v>2254</v>
       </c>
-      <c r="V506" s="5"/>
-      <c r="W506" s="5"/>
+      <c r="V506" s="5" t="n">
+        <v>-3.772331</v>
+      </c>
+      <c r="W506" s="5" t="n">
+        <v>-38.479214</v>
+      </c>
     </row>
     <row r="507" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A507" s="5" t="s">
@@ -38430,10 +38770,10 @@
         <v>2258</v>
       </c>
       <c r="V507" s="5" t="n">
-        <v>-3.7183779</v>
+        <v>-3.718576</v>
       </c>
       <c r="W507" s="5" t="n">
-        <v>-38.5785668</v>
+        <v>-38.579745</v>
       </c>
     </row>
     <row r="508" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38488,8 +38828,12 @@
       <c r="U508" s="5" t="s">
         <v>2262</v>
       </c>
-      <c r="V508" s="5"/>
-      <c r="W508" s="5"/>
+      <c r="V508" s="5" t="n">
+        <v>-3.725214</v>
+      </c>
+      <c r="W508" s="5" t="n">
+        <v>-38.466285</v>
+      </c>
     </row>
     <row r="509" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A509" s="5" t="s">
@@ -38552,10 +38896,10 @@
         <v>2267</v>
       </c>
       <c r="V509" s="5" t="n">
-        <v>-3.8475644</v>
+        <v>-3.851001</v>
       </c>
       <c r="W509" s="5" t="n">
-        <v>-38.5283559</v>
+        <v>-38.524773</v>
       </c>
     </row>
     <row r="510" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38612,8 +38956,12 @@
       <c r="U510" s="5" t="s">
         <v>2271</v>
       </c>
-      <c r="V510" s="5"/>
-      <c r="W510" s="5"/>
+      <c r="V510" s="5" t="n">
+        <v>-3.784059</v>
+      </c>
+      <c r="W510" s="5" t="n">
+        <v>-38.498545</v>
+      </c>
     </row>
     <row r="511" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A511" s="5" t="s">
@@ -38668,10 +39016,10 @@
         <v>2275</v>
       </c>
       <c r="V511" s="5" t="n">
-        <v>-3.8044349</v>
+        <v>-3.804449</v>
       </c>
       <c r="W511" s="5" t="n">
-        <v>-38.605756</v>
+        <v>-38.605757</v>
       </c>
     </row>
     <row r="512" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38727,10 +39075,10 @@
         <v>2279</v>
       </c>
       <c r="V512" s="5" t="n">
-        <v>-3.8291029</v>
+        <v>-3.827391</v>
       </c>
       <c r="W512" s="5" t="n">
-        <v>-38.5283474</v>
+        <v>-38.533256</v>
       </c>
     </row>
     <row r="513" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -38786,10 +39134,10 @@
         <v>2283</v>
       </c>
       <c r="V513" s="5" t="n">
-        <v>-3.8573858</v>
+        <v>-3.856931</v>
       </c>
       <c r="W513" s="5" t="n">
-        <v>-38.4877475</v>
+        <v>-38.488691</v>
       </c>
     </row>
   </sheetData>
@@ -66070,7 +66418,7 @@
       </c>
       <c r="B12" s="13" t="n">
         <f aca="false">COUNTA(ESCOLA!V2:V513)</f>
-        <v>425</v>
+        <v>512</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
